--- a/Data/2021_F013B4_CO_ISSWC/2021_F013B4_CO_ISSWC_SoilAnalysis.xlsx
+++ b/Data/2021_F013B4_CO_ISSWC/2021_F013B4_CO_ISSWC_SoilAnalysis.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\mnt\Data1\USDA-ALARC\GIS\PDI project\cottondata\Data\2021_F013B4_CO_ISSWC\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D1A6DE7F-4C1E-4FEE-AEAB-927753323F75}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{98C3B4CA-EBE2-4CEA-9EE4-62DF68B48BE1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-1470" yWindow="-25680" windowWidth="17805" windowHeight="20370" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="16335" yWindow="-27780" windowWidth="18210" windowHeight="27570" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="SoilDF" sheetId="2" r:id="rId1"/>
@@ -778,9 +778,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="2">
+  <numFmts count="3">
     <numFmt numFmtId="164" formatCode="0.000"/>
-    <numFmt numFmtId="166" formatCode="mm/dd/yyyy"/>
+    <numFmt numFmtId="165" formatCode="mm/dd/yyyy"/>
+    <numFmt numFmtId="166" formatCode="0.0"/>
   </numFmts>
   <fonts count="18" x14ac:knownFonts="1">
     <font>
@@ -1265,14 +1266,16 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="16" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="2" fontId="0" fillId="33" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="42">
     <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -1765,52 +1768,52 @@
       <c r="E3">
         <v>20</v>
       </c>
-      <c r="F3">
+      <c r="F3" s="7">
         <v>8.3000000000000007</v>
       </c>
-      <c r="G3">
+      <c r="G3" s="7">
         <v>7.2</v>
       </c>
-      <c r="H3">
+      <c r="H3" s="3">
         <v>0.82</v>
       </c>
-      <c r="I3">
+      <c r="I3" s="7">
         <v>1.2</v>
       </c>
-      <c r="J3">
+      <c r="J3" s="7">
         <v>1.7</v>
       </c>
-      <c r="K3">
+      <c r="K3" s="7">
         <v>3.7</v>
       </c>
-      <c r="L3">
+      <c r="L3" s="8">
         <v>338</v>
       </c>
-      <c r="M3">
+      <c r="M3" s="7">
         <v>79</v>
       </c>
-      <c r="N3">
+      <c r="N3" s="3">
         <v>2.16</v>
       </c>
-      <c r="O3">
+      <c r="O3" s="7">
         <v>7.1</v>
       </c>
-      <c r="P3">
+      <c r="P3" s="7">
         <v>10.7</v>
       </c>
-      <c r="Q3">
+      <c r="Q3" s="3">
         <v>2.92</v>
       </c>
-      <c r="R3">
+      <c r="R3" s="8">
         <v>3188</v>
       </c>
-      <c r="S3">
+      <c r="S3" s="8">
         <v>269</v>
       </c>
-      <c r="T3">
+      <c r="T3" s="8">
         <v>646</v>
       </c>
-      <c r="U3">
+      <c r="U3" s="7">
         <v>21.9</v>
       </c>
     </row>
@@ -1830,52 +1833,52 @@
       <c r="E4">
         <v>60</v>
       </c>
-      <c r="F4">
+      <c r="F4" s="7">
         <v>8.5</v>
       </c>
-      <c r="G4">
+      <c r="G4" s="7">
         <v>7.2</v>
       </c>
-      <c r="H4">
+      <c r="H4" s="3">
         <v>0.65</v>
       </c>
-      <c r="I4">
+      <c r="I4" s="7">
         <v>1.1000000000000001</v>
       </c>
-      <c r="J4">
+      <c r="J4" s="7">
         <v>5.2</v>
       </c>
-      <c r="K4">
+      <c r="K4" s="7">
         <v>6</v>
       </c>
-      <c r="L4">
+      <c r="L4" s="8">
         <v>262</v>
       </c>
-      <c r="M4">
+      <c r="M4" s="7">
         <v>85.3</v>
       </c>
-      <c r="N4">
+      <c r="N4" s="3">
         <v>2.64</v>
       </c>
-      <c r="O4">
+      <c r="O4" s="7">
         <v>6.8</v>
       </c>
-      <c r="P4">
+      <c r="P4" s="7">
         <v>9.1</v>
       </c>
-      <c r="Q4">
+      <c r="Q4" s="3">
         <v>2.3199999999999998</v>
       </c>
-      <c r="R4">
+      <c r="R4" s="8">
         <v>4164</v>
       </c>
-      <c r="S4">
+      <c r="S4" s="8">
         <v>271</v>
       </c>
-      <c r="T4">
+      <c r="T4" s="8">
         <v>625</v>
       </c>
-      <c r="U4">
+      <c r="U4" s="7">
         <v>26.5</v>
       </c>
     </row>
@@ -1895,52 +1898,52 @@
       <c r="E5">
         <v>100</v>
       </c>
-      <c r="F5">
+      <c r="F5" s="7">
         <v>8.3000000000000007</v>
       </c>
-      <c r="G5">
+      <c r="G5" s="7">
         <v>7.2</v>
       </c>
-      <c r="H5">
+      <c r="H5" s="3">
         <v>0.99</v>
       </c>
-      <c r="I5">
+      <c r="I5" s="7">
         <v>1</v>
       </c>
-      <c r="J5">
+      <c r="J5" s="7">
         <v>11</v>
       </c>
-      <c r="K5">
+      <c r="K5" s="7">
         <v>10.7</v>
       </c>
-      <c r="L5">
+      <c r="L5" s="8">
         <v>269</v>
       </c>
-      <c r="M5">
+      <c r="M5" s="7">
         <v>130.80000000000001</v>
       </c>
-      <c r="N5">
+      <c r="N5" s="3">
         <v>3.08</v>
       </c>
-      <c r="O5">
+      <c r="O5" s="7">
         <v>6.8</v>
       </c>
-      <c r="P5">
+      <c r="P5" s="7">
         <v>9.1</v>
       </c>
-      <c r="Q5">
+      <c r="Q5" s="3">
         <v>2.09</v>
       </c>
-      <c r="R5">
+      <c r="R5" s="8">
         <v>4435</v>
       </c>
-      <c r="S5">
+      <c r="S5" s="8">
         <v>287</v>
       </c>
-      <c r="T5">
+      <c r="T5" s="8">
         <v>734</v>
       </c>
-      <c r="U5">
+      <c r="U5" s="7">
         <v>28.4</v>
       </c>
     </row>
@@ -1960,52 +1963,52 @@
       <c r="E6">
         <v>140</v>
       </c>
-      <c r="F6">
+      <c r="F6" s="7">
         <v>8.3000000000000007</v>
       </c>
-      <c r="G6">
+      <c r="G6" s="7">
         <v>7.2</v>
       </c>
-      <c r="H6">
+      <c r="H6" s="3">
         <v>0.9</v>
       </c>
-      <c r="I6">
+      <c r="I6" s="7">
         <v>1</v>
       </c>
-      <c r="J6">
+      <c r="J6" s="7">
         <v>4.8</v>
       </c>
-      <c r="K6">
+      <c r="K6" s="7">
         <v>6.2</v>
       </c>
-      <c r="L6">
+      <c r="L6" s="8">
         <v>249</v>
       </c>
-      <c r="M6">
+      <c r="M6" s="7">
         <v>91</v>
       </c>
-      <c r="N6">
+      <c r="N6" s="3">
         <v>2.54</v>
       </c>
-      <c r="O6">
+      <c r="O6" s="7">
         <v>6</v>
       </c>
-      <c r="P6">
+      <c r="P6" s="7">
         <v>7.8</v>
       </c>
-      <c r="Q6">
+      <c r="Q6" s="3">
         <v>1.81</v>
       </c>
-      <c r="R6">
+      <c r="R6" s="8">
         <v>4205</v>
       </c>
-      <c r="S6">
+      <c r="S6" s="8">
         <v>296</v>
       </c>
-      <c r="T6">
+      <c r="T6" s="8">
         <v>580</v>
       </c>
-      <c r="U6">
+      <c r="U6" s="7">
         <v>26.7</v>
       </c>
     </row>
@@ -2025,52 +2028,52 @@
       <c r="E7">
         <v>180</v>
       </c>
-      <c r="F7">
+      <c r="F7" s="7">
         <v>8.3000000000000007</v>
       </c>
-      <c r="G7">
+      <c r="G7" s="7">
         <v>7.2</v>
       </c>
-      <c r="H7">
+      <c r="H7" s="3">
         <v>0.76</v>
       </c>
-      <c r="I7">
+      <c r="I7" s="7">
         <v>0.7</v>
       </c>
-      <c r="J7">
+      <c r="J7" s="7">
         <v>5.2</v>
       </c>
-      <c r="K7">
+      <c r="K7" s="7">
         <v>6</v>
       </c>
-      <c r="L7">
+      <c r="L7" s="8">
         <v>138</v>
       </c>
-      <c r="M7">
+      <c r="M7" s="7">
         <v>82.9</v>
       </c>
-      <c r="N7">
+      <c r="N7" s="3">
         <v>2.37</v>
       </c>
-      <c r="O7">
+      <c r="O7" s="7">
         <v>4.7</v>
       </c>
-      <c r="P7">
+      <c r="P7" s="7">
         <v>2.9</v>
       </c>
-      <c r="Q7">
+      <c r="Q7" s="3">
         <v>0.71</v>
       </c>
-      <c r="R7">
+      <c r="R7" s="8">
         <v>4000</v>
       </c>
-      <c r="S7">
+      <c r="S7" s="8">
         <v>269</v>
       </c>
-      <c r="T7">
+      <c r="T7" s="8">
         <v>418</v>
       </c>
-      <c r="U7">
+      <c r="U7" s="7">
         <v>24.4</v>
       </c>
     </row>
@@ -2090,52 +2093,52 @@
       <c r="E8">
         <v>20</v>
       </c>
-      <c r="F8">
+      <c r="F8" s="7">
         <v>8.3000000000000007</v>
       </c>
-      <c r="G8">
+      <c r="G8" s="7">
         <v>7.2</v>
       </c>
-      <c r="H8">
+      <c r="H8" s="3">
         <v>0.65</v>
       </c>
-      <c r="I8">
+      <c r="I8" s="7">
         <v>1.2</v>
       </c>
-      <c r="J8">
+      <c r="J8" s="7">
         <v>1.1000000000000001</v>
       </c>
-      <c r="K8">
+      <c r="K8" s="7">
         <v>4</v>
       </c>
-      <c r="L8">
+      <c r="L8" s="8">
         <v>348</v>
       </c>
-      <c r="M8">
+      <c r="M8" s="7">
         <v>117.2</v>
       </c>
-      <c r="N8">
+      <c r="N8" s="3">
         <v>1.58</v>
       </c>
-      <c r="O8">
+      <c r="O8" s="7">
         <v>7.5</v>
       </c>
-      <c r="P8">
+      <c r="P8" s="7">
         <v>9</v>
       </c>
-      <c r="Q8">
+      <c r="Q8" s="3">
         <v>3.15</v>
       </c>
-      <c r="R8">
+      <c r="R8" s="8">
         <v>3427</v>
       </c>
-      <c r="S8">
+      <c r="S8" s="8">
         <v>309</v>
       </c>
-      <c r="T8">
+      <c r="T8" s="8">
         <v>648</v>
       </c>
-      <c r="U8">
+      <c r="U8" s="7">
         <v>23.4</v>
       </c>
     </row>
@@ -2155,52 +2158,52 @@
       <c r="E9">
         <v>60</v>
       </c>
-      <c r="F9">
+      <c r="F9" s="7">
         <v>8.6</v>
       </c>
-      <c r="G9">
+      <c r="G9" s="7">
         <v>7.2</v>
       </c>
-      <c r="H9">
+      <c r="H9" s="3">
         <v>0.76</v>
       </c>
-      <c r="I9">
+      <c r="I9" s="7">
         <v>0.7</v>
       </c>
-      <c r="J9">
+      <c r="J9" s="7">
         <v>2.2000000000000002</v>
       </c>
-      <c r="K9">
+      <c r="K9" s="7">
         <v>4.0999999999999996</v>
       </c>
-      <c r="L9">
+      <c r="L9" s="8">
         <v>193</v>
       </c>
-      <c r="M9">
+      <c r="M9" s="7">
         <v>81.3</v>
       </c>
-      <c r="N9">
+      <c r="N9" s="3">
         <v>0.9</v>
       </c>
-      <c r="O9">
+      <c r="O9" s="7">
         <v>6.7</v>
       </c>
-      <c r="P9">
+      <c r="P9" s="7">
         <v>5.5</v>
       </c>
-      <c r="Q9">
+      <c r="Q9" s="3">
         <v>1.99</v>
       </c>
-      <c r="R9">
+      <c r="R9" s="8">
         <v>3852</v>
       </c>
-      <c r="S9">
+      <c r="S9" s="8">
         <v>310</v>
       </c>
-      <c r="T9">
+      <c r="T9" s="8">
         <v>779</v>
       </c>
-      <c r="U9">
+      <c r="U9" s="7">
         <v>25.7</v>
       </c>
     </row>
@@ -2220,52 +2223,52 @@
       <c r="E10">
         <v>100</v>
       </c>
-      <c r="F10">
+      <c r="F10" s="7">
         <v>8.4</v>
       </c>
-      <c r="G10">
+      <c r="G10" s="7">
         <v>7.2</v>
       </c>
-      <c r="H10">
+      <c r="H10" s="3">
         <v>1.3</v>
       </c>
-      <c r="I10">
+      <c r="I10" s="7">
         <v>0.7</v>
       </c>
-      <c r="J10">
+      <c r="J10" s="7">
         <v>3.5</v>
       </c>
-      <c r="K10">
+      <c r="K10" s="7">
         <v>3.8</v>
       </c>
-      <c r="L10">
+      <c r="L10" s="8">
         <v>150</v>
       </c>
-      <c r="M10">
+      <c r="M10" s="7">
         <v>207.2</v>
       </c>
-      <c r="N10">
+      <c r="N10" s="3">
         <v>0.57999999999999996</v>
       </c>
-      <c r="O10">
+      <c r="O10" s="7">
         <v>4.5</v>
       </c>
-      <c r="P10">
+      <c r="P10" s="7">
         <v>2.7</v>
       </c>
-      <c r="Q10">
+      <c r="Q10" s="3">
         <v>0.89</v>
       </c>
-      <c r="R10">
+      <c r="R10" s="8">
         <v>4532</v>
       </c>
-      <c r="S10">
+      <c r="S10" s="8">
         <v>351</v>
       </c>
-      <c r="T10">
+      <c r="T10" s="8">
         <v>947</v>
       </c>
-      <c r="U10">
+      <c r="U10" s="7">
         <v>30.1</v>
       </c>
     </row>
@@ -2285,52 +2288,52 @@
       <c r="E11">
         <v>140</v>
       </c>
-      <c r="F11">
+      <c r="F11" s="7">
         <v>8.4</v>
       </c>
-      <c r="G11">
+      <c r="G11" s="7">
         <v>7.2</v>
       </c>
-      <c r="H11">
+      <c r="H11" s="3">
         <v>1.01</v>
       </c>
-      <c r="I11">
+      <c r="I11" s="7">
         <v>0.6</v>
       </c>
-      <c r="J11">
+      <c r="J11" s="7">
         <v>1.7</v>
       </c>
-      <c r="K11">
+      <c r="K11" s="7">
         <v>4.9000000000000004</v>
       </c>
-      <c r="L11">
+      <c r="L11" s="8">
         <v>106</v>
       </c>
-      <c r="M11">
+      <c r="M11" s="7">
         <v>92.9</v>
       </c>
-      <c r="N11">
+      <c r="N11" s="3">
         <v>0.43</v>
       </c>
-      <c r="O11">
+      <c r="O11" s="7">
         <v>3.5</v>
       </c>
-      <c r="P11">
+      <c r="P11" s="7">
         <v>2.2000000000000002</v>
       </c>
-      <c r="Q11">
+      <c r="Q11" s="3">
         <v>0.52</v>
       </c>
-      <c r="R11">
+      <c r="R11" s="8">
         <v>4221</v>
       </c>
-      <c r="S11">
+      <c r="S11" s="8">
         <v>263</v>
       </c>
-      <c r="T11">
+      <c r="T11" s="8">
         <v>540</v>
       </c>
-      <c r="U11">
+      <c r="U11" s="7">
         <v>25.9</v>
       </c>
     </row>
@@ -2350,52 +2353,52 @@
       <c r="E12">
         <v>180</v>
       </c>
-      <c r="F12">
+      <c r="F12" s="7">
         <v>8.5</v>
       </c>
-      <c r="G12">
+      <c r="G12" s="7">
         <v>7.2</v>
       </c>
-      <c r="H12">
+      <c r="H12" s="3">
         <v>0.56999999999999995</v>
       </c>
-      <c r="I12">
+      <c r="I12" s="7">
         <v>0.5</v>
       </c>
-      <c r="J12">
+      <c r="J12" s="7">
         <v>0.9</v>
       </c>
-      <c r="K12">
+      <c r="K12" s="7">
         <v>4.0999999999999996</v>
       </c>
-      <c r="L12">
+      <c r="L12" s="8">
         <v>96</v>
       </c>
-      <c r="M12">
+      <c r="M12" s="7">
         <v>48.9</v>
       </c>
-      <c r="N12">
+      <c r="N12" s="3">
         <v>0.83</v>
       </c>
-      <c r="O12">
+      <c r="O12" s="7">
         <v>4.0999999999999996</v>
       </c>
-      <c r="P12">
+      <c r="P12" s="7">
         <v>2.1</v>
       </c>
-      <c r="Q12">
+      <c r="Q12" s="3">
         <v>0.5</v>
       </c>
-      <c r="R12">
+      <c r="R12" s="8">
         <v>3705</v>
       </c>
-      <c r="S12">
+      <c r="S12" s="8">
         <v>225</v>
       </c>
-      <c r="T12">
+      <c r="T12" s="8">
         <v>326</v>
       </c>
-      <c r="U12">
+      <c r="U12" s="7">
         <v>22.1</v>
       </c>
     </row>
@@ -2415,52 +2418,52 @@
       <c r="E13">
         <v>20</v>
       </c>
-      <c r="F13">
+      <c r="F13" s="7">
         <v>8.4</v>
       </c>
-      <c r="G13">
+      <c r="G13" s="7">
         <v>7.2</v>
       </c>
-      <c r="H13">
+      <c r="H13" s="3">
         <v>0.49</v>
       </c>
-      <c r="I13">
+      <c r="I13" s="7">
         <v>1.3</v>
       </c>
-      <c r="J13">
+      <c r="J13" s="7">
         <v>0.7</v>
       </c>
-      <c r="K13">
+      <c r="K13" s="7">
         <v>4.2</v>
       </c>
-      <c r="L13">
+      <c r="L13" s="8">
         <v>349</v>
       </c>
-      <c r="M13">
+      <c r="M13" s="7">
         <v>55.7</v>
       </c>
-      <c r="N13">
+      <c r="N13" s="3">
         <v>1.81</v>
       </c>
-      <c r="O13">
+      <c r="O13" s="7">
         <v>7.3</v>
       </c>
-      <c r="P13">
+      <c r="P13" s="7">
         <v>9.6</v>
       </c>
-      <c r="Q13">
+      <c r="Q13" s="3">
         <v>2.78</v>
       </c>
-      <c r="R13">
+      <c r="R13" s="8">
         <v>2804</v>
       </c>
-      <c r="S13">
+      <c r="S13" s="8">
         <v>272</v>
       </c>
-      <c r="T13">
+      <c r="T13" s="8">
         <v>470</v>
       </c>
-      <c r="U13">
+      <c r="U13" s="7">
         <v>19.2</v>
       </c>
     </row>
@@ -2480,52 +2483,52 @@
       <c r="E14">
         <v>60</v>
       </c>
-      <c r="F14">
+      <c r="F14" s="7">
         <v>8.9</v>
       </c>
-      <c r="G14">
+      <c r="G14" s="7">
         <v>7.2</v>
       </c>
-      <c r="H14">
+      <c r="H14" s="3">
         <v>0.54</v>
       </c>
-      <c r="I14">
+      <c r="I14" s="7">
         <v>0.8</v>
       </c>
-      <c r="J14">
+      <c r="J14" s="7">
         <v>1</v>
       </c>
-      <c r="K14">
+      <c r="K14" s="7">
         <v>4.9000000000000004</v>
       </c>
-      <c r="L14">
+      <c r="L14" s="8">
         <v>219</v>
       </c>
-      <c r="M14">
+      <c r="M14" s="7">
         <v>55.4</v>
       </c>
-      <c r="N14">
+      <c r="N14" s="3">
         <v>0.71</v>
       </c>
-      <c r="O14">
+      <c r="O14" s="7">
         <v>6.2</v>
       </c>
-      <c r="P14">
+      <c r="P14" s="7">
         <v>7.3</v>
       </c>
-      <c r="Q14">
+      <c r="Q14" s="3">
         <v>1.87</v>
       </c>
-      <c r="R14">
+      <c r="R14" s="8">
         <v>3701</v>
       </c>
-      <c r="S14">
+      <c r="S14" s="8">
         <v>251</v>
       </c>
-      <c r="T14">
+      <c r="T14" s="8">
         <v>701</v>
       </c>
-      <c r="U14">
+      <c r="U14" s="7">
         <v>24.2</v>
       </c>
     </row>
@@ -2545,52 +2548,52 @@
       <c r="E15">
         <v>100</v>
       </c>
-      <c r="F15">
+      <c r="F15" s="7">
         <v>8.6999999999999993</v>
       </c>
-      <c r="G15">
+      <c r="G15" s="7">
         <v>7.2</v>
       </c>
-      <c r="H15">
+      <c r="H15" s="3">
         <v>0.63</v>
       </c>
-      <c r="I15">
+      <c r="I15" s="7">
         <v>0.6</v>
       </c>
-      <c r="J15">
+      <c r="J15" s="7">
         <v>1.8</v>
       </c>
-      <c r="K15">
+      <c r="K15" s="7">
         <v>4.5</v>
       </c>
-      <c r="L15">
+      <c r="L15" s="8">
         <v>169</v>
       </c>
-      <c r="M15">
+      <c r="M15" s="7">
         <v>84.8</v>
       </c>
-      <c r="N15">
+      <c r="N15" s="3">
         <v>0.34</v>
       </c>
-      <c r="O15">
+      <c r="O15" s="7">
         <v>4.5</v>
       </c>
-      <c r="P15">
+      <c r="P15" s="7">
         <v>3.5</v>
       </c>
-      <c r="Q15">
+      <c r="Q15" s="3">
         <v>1.1399999999999999</v>
       </c>
-      <c r="R15">
+      <c r="R15" s="8">
         <v>3928</v>
       </c>
-      <c r="S15">
+      <c r="S15" s="8">
         <v>243</v>
       </c>
-      <c r="T15">
+      <c r="T15" s="8">
         <v>596</v>
       </c>
-      <c r="U15">
+      <c r="U15" s="7">
         <v>24.7</v>
       </c>
     </row>
@@ -2610,52 +2613,52 @@
       <c r="E16">
         <v>140</v>
       </c>
-      <c r="F16">
+      <c r="F16" s="7">
         <v>8.4</v>
       </c>
-      <c r="G16">
+      <c r="G16" s="7">
         <v>7.2</v>
       </c>
-      <c r="H16">
+      <c r="H16" s="3">
         <v>0.81</v>
       </c>
-      <c r="I16">
+      <c r="I16" s="7">
         <v>0.7</v>
       </c>
-      <c r="J16">
+      <c r="J16" s="7">
         <v>5.2</v>
       </c>
-      <c r="K16">
+      <c r="K16" s="7">
         <v>4.0999999999999996</v>
       </c>
-      <c r="L16">
+      <c r="L16" s="8">
         <v>143</v>
       </c>
-      <c r="M16">
+      <c r="M16" s="7">
         <v>154.9</v>
       </c>
-      <c r="N16">
+      <c r="N16" s="3">
         <v>0.25</v>
       </c>
-      <c r="O16">
+      <c r="O16" s="7">
         <v>4</v>
       </c>
-      <c r="P16">
+      <c r="P16" s="7">
         <v>1.9</v>
       </c>
-      <c r="Q16">
+      <c r="Q16" s="3">
         <v>0.55000000000000004</v>
       </c>
-      <c r="R16">
+      <c r="R16" s="8">
         <v>4302</v>
       </c>
-      <c r="S16">
+      <c r="S16" s="8">
         <v>288</v>
       </c>
-      <c r="T16">
+      <c r="T16" s="8">
         <v>514</v>
       </c>
-      <c r="U16">
+      <c r="U16" s="7">
         <v>26.5</v>
       </c>
     </row>
@@ -2675,52 +2678,52 @@
       <c r="E17">
         <v>180</v>
       </c>
-      <c r="F17">
+      <c r="F17" s="7">
         <v>8.4</v>
       </c>
-      <c r="G17">
+      <c r="G17" s="7">
         <v>7.2</v>
       </c>
-      <c r="H17">
+      <c r="H17" s="3">
         <v>0.9</v>
       </c>
-      <c r="I17">
+      <c r="I17" s="7">
         <v>0.7</v>
       </c>
-      <c r="J17">
+      <c r="J17" s="7">
         <v>2.1</v>
       </c>
-      <c r="K17">
+      <c r="K17" s="7">
         <v>3.4</v>
       </c>
-      <c r="L17">
+      <c r="L17" s="8">
         <v>133</v>
       </c>
-      <c r="M17">
+      <c r="M17" s="7">
         <v>107.7</v>
       </c>
-      <c r="N17">
+      <c r="N17" s="3">
         <v>0.37</v>
       </c>
-      <c r="O17">
+      <c r="O17" s="7">
         <v>4.8</v>
       </c>
-      <c r="P17">
+      <c r="P17" s="7">
         <v>3.3</v>
       </c>
-      <c r="Q17">
+      <c r="Q17" s="3">
         <v>0.59</v>
       </c>
-      <c r="R17">
+      <c r="R17" s="8">
         <v>4127</v>
       </c>
-      <c r="S17">
+      <c r="S17" s="8">
         <v>259</v>
       </c>
-      <c r="T17">
+      <c r="T17" s="8">
         <v>338</v>
       </c>
-      <c r="U17">
+      <c r="U17" s="7">
         <v>24.6</v>
       </c>
     </row>
@@ -2740,52 +2743,52 @@
       <c r="E18">
         <v>20</v>
       </c>
-      <c r="F18">
+      <c r="F18" s="7">
         <v>8.5</v>
       </c>
-      <c r="G18">
+      <c r="G18" s="7">
         <v>7.2</v>
       </c>
-      <c r="H18">
+      <c r="H18" s="3">
         <v>0.53</v>
       </c>
-      <c r="I18">
+      <c r="I18" s="7">
         <v>1.1000000000000001</v>
       </c>
-      <c r="J18">
+      <c r="J18" s="7">
         <v>0.9</v>
       </c>
-      <c r="K18">
+      <c r="K18" s="7">
         <v>3.8</v>
       </c>
-      <c r="L18">
+      <c r="L18" s="8">
         <v>295</v>
       </c>
-      <c r="M18">
+      <c r="M18" s="7">
         <v>33.700000000000003</v>
       </c>
-      <c r="N18">
+      <c r="N18" s="3">
         <v>1.42</v>
       </c>
-      <c r="O18">
+      <c r="O18" s="7">
         <v>7.5</v>
       </c>
-      <c r="P18">
+      <c r="P18" s="7">
         <v>11.1</v>
       </c>
-      <c r="Q18">
+      <c r="Q18" s="3">
         <v>3.16</v>
       </c>
-      <c r="R18">
+      <c r="R18" s="8">
         <v>2958</v>
       </c>
-      <c r="S18">
+      <c r="S18" s="8">
         <v>262</v>
       </c>
-      <c r="T18">
+      <c r="T18" s="8">
         <v>408</v>
       </c>
-      <c r="U18">
+      <c r="U18" s="7">
         <v>19.5</v>
       </c>
     </row>
@@ -2805,52 +2808,52 @@
       <c r="E19">
         <v>60</v>
       </c>
-      <c r="F19">
+      <c r="F19" s="7">
         <v>8.6</v>
       </c>
-      <c r="G19">
+      <c r="G19" s="7">
         <v>7.2</v>
       </c>
-      <c r="H19">
+      <c r="H19" s="3">
         <v>0.9</v>
       </c>
-      <c r="I19">
+      <c r="I19" s="7">
         <v>0.7</v>
       </c>
-      <c r="J19">
+      <c r="J19" s="7">
         <v>0.6</v>
       </c>
-      <c r="K19">
+      <c r="K19" s="7">
         <v>5.3</v>
       </c>
-      <c r="L19">
+      <c r="L19" s="8">
         <v>238</v>
       </c>
-      <c r="M19">
+      <c r="M19" s="7">
         <v>112.9</v>
       </c>
-      <c r="N19">
+      <c r="N19" s="3">
         <v>1.17</v>
       </c>
-      <c r="O19">
+      <c r="O19" s="7">
         <v>9.1999999999999993</v>
       </c>
-      <c r="P19">
+      <c r="P19" s="7">
         <v>9.3000000000000007</v>
       </c>
-      <c r="Q19">
+      <c r="Q19" s="3">
         <v>2.06</v>
       </c>
-      <c r="R19">
+      <c r="R19" s="8">
         <v>4317</v>
       </c>
-      <c r="S19">
+      <c r="S19" s="8">
         <v>325</v>
       </c>
-      <c r="T19">
+      <c r="T19" s="8">
         <v>835</v>
       </c>
-      <c r="U19">
+      <c r="U19" s="7">
         <v>28.5</v>
       </c>
     </row>
@@ -2870,52 +2873,52 @@
       <c r="E20">
         <v>100</v>
       </c>
-      <c r="F20">
+      <c r="F20" s="7">
         <v>8.4</v>
       </c>
-      <c r="G20">
+      <c r="G20" s="7">
         <v>7.2</v>
       </c>
-      <c r="H20">
+      <c r="H20" s="3">
         <v>1.1599999999999999</v>
       </c>
-      <c r="I20">
+      <c r="I20" s="7">
         <v>0.7</v>
       </c>
-      <c r="J20">
+      <c r="J20" s="7">
         <v>4.4000000000000004</v>
       </c>
-      <c r="K20">
+      <c r="K20" s="7">
         <v>4.2</v>
       </c>
-      <c r="L20">
+      <c r="L20" s="8">
         <v>161</v>
       </c>
-      <c r="M20">
+      <c r="M20" s="7">
         <v>177.1</v>
       </c>
-      <c r="N20">
+      <c r="N20" s="3">
         <v>0.52</v>
       </c>
-      <c r="O20">
+      <c r="O20" s="7">
         <v>6.6</v>
       </c>
-      <c r="P20">
+      <c r="P20" s="7">
         <v>6</v>
       </c>
-      <c r="Q20">
+      <c r="Q20" s="3">
         <v>1.1599999999999999</v>
       </c>
-      <c r="R20">
+      <c r="R20" s="8">
         <v>4303</v>
       </c>
-      <c r="S20">
+      <c r="S20" s="8">
         <v>310</v>
       </c>
-      <c r="T20">
+      <c r="T20" s="8">
         <v>631</v>
       </c>
-      <c r="U20">
+      <c r="U20" s="7">
         <v>27.3</v>
       </c>
     </row>
@@ -2935,52 +2938,52 @@
       <c r="E21">
         <v>140</v>
       </c>
-      <c r="F21">
+      <c r="F21" s="7">
         <v>8.3000000000000007</v>
       </c>
-      <c r="G21">
+      <c r="G21" s="7">
         <v>7.2</v>
       </c>
-      <c r="H21">
+      <c r="H21" s="3">
         <v>1.25</v>
       </c>
-      <c r="I21">
+      <c r="I21" s="7">
         <v>0.7</v>
       </c>
-      <c r="J21">
+      <c r="J21" s="7">
         <v>9.6</v>
       </c>
-      <c r="K21">
+      <c r="K21" s="7">
         <v>4</v>
       </c>
-      <c r="L21">
+      <c r="L21" s="8">
         <v>127</v>
       </c>
-      <c r="M21">
+      <c r="M21" s="7">
         <v>108.1</v>
       </c>
-      <c r="N21">
+      <c r="N21" s="3">
         <v>0.4</v>
       </c>
-      <c r="O21">
+      <c r="O21" s="7">
         <v>6.5</v>
       </c>
-      <c r="P21">
+      <c r="P21" s="7">
         <v>4.2</v>
       </c>
-      <c r="Q21">
+      <c r="Q21" s="3">
         <v>0.77</v>
       </c>
-      <c r="R21">
+      <c r="R21" s="8">
         <v>4267</v>
       </c>
-      <c r="S21">
+      <c r="S21" s="8">
         <v>287</v>
       </c>
-      <c r="T21">
+      <c r="T21" s="8">
         <v>446</v>
       </c>
-      <c r="U21">
+      <c r="U21" s="7">
         <v>26</v>
       </c>
     </row>
@@ -3000,52 +3003,52 @@
       <c r="E22">
         <v>180</v>
       </c>
-      <c r="F22">
+      <c r="F22" s="7">
         <v>8.3000000000000007</v>
       </c>
-      <c r="G22">
+      <c r="G22" s="7">
         <v>7.2</v>
       </c>
-      <c r="H22">
+      <c r="H22" s="3">
         <v>0.82</v>
       </c>
-      <c r="I22">
+      <c r="I22" s="7">
         <v>0.6</v>
       </c>
-      <c r="J22">
+      <c r="J22" s="7">
         <v>4</v>
       </c>
-      <c r="K22">
+      <c r="K22" s="7">
         <v>3.4</v>
       </c>
-      <c r="L22">
+      <c r="L22" s="8">
         <v>111</v>
       </c>
-      <c r="M22">
+      <c r="M22" s="7">
         <v>70.3</v>
       </c>
-      <c r="N22">
+      <c r="N22" s="3">
         <v>0.49</v>
       </c>
-      <c r="O22">
+      <c r="O22" s="7">
         <v>7.6</v>
       </c>
-      <c r="P22">
+      <c r="P22" s="7">
         <v>5.5</v>
       </c>
-      <c r="Q22">
+      <c r="Q22" s="3">
         <v>0.81</v>
       </c>
-      <c r="R22">
+      <c r="R22" s="8">
         <v>3832</v>
       </c>
-      <c r="S22">
+      <c r="S22" s="8">
         <v>226</v>
       </c>
-      <c r="T22">
+      <c r="T22" s="8">
         <v>274</v>
       </c>
-      <c r="U22">
+      <c r="U22" s="7">
         <v>22.5</v>
       </c>
     </row>
@@ -3065,52 +3068,52 @@
       <c r="E23">
         <v>20</v>
       </c>
-      <c r="F23">
+      <c r="F23" s="7">
         <v>8.3000000000000007</v>
       </c>
-      <c r="G23">
+      <c r="G23" s="7">
         <v>7.2</v>
       </c>
-      <c r="H23">
+      <c r="H23" s="3">
         <v>1</v>
       </c>
-      <c r="I23">
+      <c r="I23" s="7">
         <v>1.4</v>
       </c>
-      <c r="J23">
+      <c r="J23" s="7">
         <v>0.7</v>
       </c>
-      <c r="K23">
+      <c r="K23" s="7">
         <v>3.9</v>
       </c>
-      <c r="L23">
+      <c r="L23" s="8">
         <v>322</v>
       </c>
-      <c r="M23">
+      <c r="M23" s="7">
         <v>76.400000000000006</v>
       </c>
-      <c r="N23">
+      <c r="N23" s="3">
         <v>1.8</v>
       </c>
-      <c r="O23">
+      <c r="O23" s="7">
         <v>7.2</v>
       </c>
-      <c r="P23">
+      <c r="P23" s="7">
         <v>11</v>
       </c>
-      <c r="Q23">
+      <c r="Q23" s="3">
         <v>2.71</v>
       </c>
-      <c r="R23">
+      <c r="R23" s="8">
         <v>2860</v>
       </c>
-      <c r="S23">
+      <c r="S23" s="8">
         <v>275</v>
       </c>
-      <c r="T23">
+      <c r="T23" s="8">
         <v>513</v>
       </c>
-      <c r="U23">
+      <c r="U23" s="7">
         <v>19.600000000000001</v>
       </c>
     </row>
@@ -3130,52 +3133,52 @@
       <c r="E24">
         <v>60</v>
       </c>
-      <c r="F24">
+      <c r="F24" s="7">
         <v>8.5</v>
       </c>
-      <c r="G24">
+      <c r="G24" s="7">
         <v>7.2</v>
       </c>
-      <c r="H24">
+      <c r="H24" s="3">
         <v>1.33</v>
       </c>
-      <c r="I24">
+      <c r="I24" s="7">
         <v>0.8</v>
       </c>
-      <c r="J24">
+      <c r="J24" s="7">
         <v>0.6</v>
       </c>
-      <c r="K24">
+      <c r="K24" s="7">
         <v>4.8</v>
       </c>
-      <c r="L24">
+      <c r="L24" s="8">
         <v>206</v>
       </c>
-      <c r="M24">
+      <c r="M24" s="7">
         <v>162.30000000000001</v>
       </c>
-      <c r="N24">
+      <c r="N24" s="3">
         <v>0.7</v>
       </c>
-      <c r="O24">
+      <c r="O24" s="7">
         <v>11.9</v>
       </c>
-      <c r="P24">
+      <c r="P24" s="7">
         <v>8.9</v>
       </c>
-      <c r="Q24">
+      <c r="Q24" s="3">
         <v>1.6</v>
       </c>
-      <c r="R24">
+      <c r="R24" s="8">
         <v>3559</v>
       </c>
-      <c r="S24">
+      <c r="S24" s="8">
         <v>299</v>
       </c>
-      <c r="T24">
+      <c r="T24" s="8">
         <v>946</v>
       </c>
-      <c r="U24">
+      <c r="U24" s="7">
         <v>24.9</v>
       </c>
     </row>
@@ -3195,52 +3198,52 @@
       <c r="E25">
         <v>100</v>
       </c>
-      <c r="F25">
+      <c r="F25" s="7">
         <v>8.4</v>
       </c>
-      <c r="G25">
+      <c r="G25" s="7">
         <v>7.2</v>
       </c>
-      <c r="H25">
+      <c r="H25" s="3">
         <v>1.25</v>
       </c>
-      <c r="I25">
+      <c r="I25" s="7">
         <v>0.9</v>
       </c>
-      <c r="J25">
+      <c r="J25" s="7">
         <v>3.1</v>
       </c>
-      <c r="K25">
+      <c r="K25" s="7">
         <v>3.5</v>
       </c>
-      <c r="L25">
+      <c r="L25" s="8">
         <v>164</v>
       </c>
-      <c r="M25">
+      <c r="M25" s="7">
         <v>173.5</v>
       </c>
-      <c r="N25">
+      <c r="N25" s="3">
         <v>0.56999999999999995</v>
       </c>
-      <c r="O25">
+      <c r="O25" s="7">
         <v>9.3000000000000007</v>
       </c>
-      <c r="P25">
+      <c r="P25" s="7">
         <v>6.3</v>
       </c>
-      <c r="Q25">
+      <c r="Q25" s="3">
         <v>1.04</v>
       </c>
-      <c r="R25">
+      <c r="R25" s="8">
         <v>4356</v>
       </c>
-      <c r="S25">
+      <c r="S25" s="8">
         <v>305</v>
       </c>
-      <c r="T25">
+      <c r="T25" s="8">
         <v>695</v>
       </c>
-      <c r="U25">
+      <c r="U25" s="7">
         <v>27.8</v>
       </c>
     </row>
@@ -3260,52 +3263,52 @@
       <c r="E26">
         <v>140</v>
       </c>
-      <c r="F26">
+      <c r="F26" s="7">
         <v>8.3000000000000007</v>
       </c>
-      <c r="G26">
+      <c r="G26" s="7">
         <v>7.2</v>
       </c>
-      <c r="H26">
+      <c r="H26" s="3">
         <v>1.08</v>
       </c>
-      <c r="I26">
+      <c r="I26" s="7">
         <v>0.8</v>
       </c>
-      <c r="J26">
+      <c r="J26" s="7">
         <v>2.7</v>
       </c>
-      <c r="K26">
+      <c r="K26" s="7">
         <v>3.7</v>
       </c>
-      <c r="L26">
+      <c r="L26" s="8">
         <v>178</v>
       </c>
-      <c r="M26">
+      <c r="M26" s="7">
         <v>141.30000000000001</v>
       </c>
-      <c r="N26">
+      <c r="N26" s="3">
         <v>0.63</v>
       </c>
-      <c r="O26">
+      <c r="O26" s="7">
         <v>7.9</v>
       </c>
-      <c r="P26">
+      <c r="P26" s="7">
         <v>5.0999999999999996</v>
       </c>
-      <c r="Q26">
+      <c r="Q26" s="3">
         <v>0.8</v>
       </c>
-      <c r="R26">
+      <c r="R26" s="8">
         <v>4406</v>
       </c>
-      <c r="S26">
+      <c r="S26" s="8">
         <v>379</v>
       </c>
-      <c r="T26">
+      <c r="T26" s="8">
         <v>574</v>
       </c>
-      <c r="U26">
+      <c r="U26" s="7">
         <v>28.1</v>
       </c>
     </row>
@@ -3325,52 +3328,52 @@
       <c r="E27">
         <v>180</v>
       </c>
-      <c r="F27">
+      <c r="F27" s="7">
         <v>8.4</v>
       </c>
-      <c r="G27">
+      <c r="G27" s="7">
         <v>7.2</v>
       </c>
-      <c r="H27">
+      <c r="H27" s="3">
         <v>0.94</v>
       </c>
-      <c r="I27">
+      <c r="I27" s="7">
         <v>0.7</v>
       </c>
-      <c r="J27">
+      <c r="J27" s="7">
         <v>1.4</v>
       </c>
-      <c r="K27">
+      <c r="K27" s="7">
         <v>4.0999999999999996</v>
       </c>
-      <c r="L27">
+      <c r="L27" s="8">
         <v>129</v>
       </c>
-      <c r="M27">
+      <c r="M27" s="7">
         <v>99.4</v>
       </c>
-      <c r="N27">
+      <c r="N27" s="3">
         <v>0.8</v>
       </c>
-      <c r="O27">
+      <c r="O27" s="7">
         <v>6.4</v>
       </c>
-      <c r="P27">
+      <c r="P27" s="7">
         <v>4.5</v>
       </c>
-      <c r="Q27">
+      <c r="Q27" s="3">
         <v>0.62</v>
       </c>
-      <c r="R27">
+      <c r="R27" s="8">
         <v>3911</v>
       </c>
-      <c r="S27">
+      <c r="S27" s="8">
         <v>321</v>
       </c>
-      <c r="T27">
+      <c r="T27" s="8">
         <v>341</v>
       </c>
-      <c r="U27">
+      <c r="U27" s="7">
         <v>24</v>
       </c>
     </row>
@@ -3390,52 +3393,52 @@
       <c r="E28">
         <v>20</v>
       </c>
-      <c r="F28">
+      <c r="F28" s="7">
         <v>8.4</v>
       </c>
-      <c r="G28">
+      <c r="G28" s="7">
         <v>7.2</v>
       </c>
-      <c r="H28">
+      <c r="H28" s="3">
         <v>1.1399999999999999</v>
       </c>
-      <c r="I28">
+      <c r="I28" s="7">
         <v>1</v>
       </c>
-      <c r="J28">
+      <c r="J28" s="7">
         <v>0.9</v>
       </c>
-      <c r="K28">
+      <c r="K28" s="7">
         <v>4</v>
       </c>
-      <c r="L28">
+      <c r="L28" s="8">
         <v>244</v>
       </c>
-      <c r="M28">
+      <c r="M28" s="7">
         <v>122.3</v>
       </c>
-      <c r="N28">
+      <c r="N28" s="3">
         <v>1.1499999999999999</v>
       </c>
-      <c r="O28">
+      <c r="O28" s="7">
         <v>5.8</v>
       </c>
-      <c r="P28">
+      <c r="P28" s="7">
         <v>8.5</v>
       </c>
-      <c r="Q28">
+      <c r="Q28" s="3">
         <v>2.5499999999999998</v>
       </c>
-      <c r="R28">
+      <c r="R28" s="8">
         <v>3122</v>
       </c>
-      <c r="S28">
+      <c r="S28" s="8">
         <v>264</v>
       </c>
-      <c r="T28">
+      <c r="T28" s="8">
         <v>658</v>
       </c>
-      <c r="U28">
+      <c r="U28" s="7">
         <v>21.3</v>
       </c>
     </row>
@@ -3455,52 +3458,52 @@
       <c r="E29">
         <v>60</v>
       </c>
-      <c r="F29">
+      <c r="F29" s="7">
         <v>8.4</v>
       </c>
-      <c r="G29">
+      <c r="G29" s="7">
         <v>7.2</v>
       </c>
-      <c r="H29">
+      <c r="H29" s="3">
         <v>1.39</v>
       </c>
-      <c r="I29">
+      <c r="I29" s="7">
         <v>0.7</v>
       </c>
-      <c r="J29">
+      <c r="J29" s="7">
         <v>4.3</v>
       </c>
-      <c r="K29">
+      <c r="K29" s="7">
         <v>5.4</v>
       </c>
-      <c r="L29">
+      <c r="L29" s="8">
         <v>154</v>
       </c>
-      <c r="M29">
+      <c r="M29" s="7">
         <v>142.30000000000001</v>
       </c>
-      <c r="N29">
+      <c r="N29" s="3">
         <v>0.45</v>
       </c>
-      <c r="O29">
+      <c r="O29" s="7">
         <v>4.8</v>
       </c>
-      <c r="P29">
+      <c r="P29" s="7">
         <v>3.9</v>
       </c>
-      <c r="Q29">
+      <c r="Q29" s="3">
         <v>1.1100000000000001</v>
       </c>
-      <c r="R29">
+      <c r="R29" s="8">
         <v>4467</v>
       </c>
-      <c r="S29">
+      <c r="S29" s="8">
         <v>329</v>
       </c>
-      <c r="T29">
+      <c r="T29" s="8">
         <v>1053</v>
       </c>
-      <c r="U29">
+      <c r="U29" s="7">
         <v>30.1</v>
       </c>
     </row>
@@ -3520,52 +3523,52 @@
       <c r="E30">
         <v>100</v>
       </c>
-      <c r="F30">
+      <c r="F30" s="7">
         <v>8.4</v>
       </c>
-      <c r="G30">
+      <c r="G30" s="7">
         <v>7.2</v>
       </c>
-      <c r="H30">
+      <c r="H30" s="3">
         <v>1.17</v>
       </c>
-      <c r="I30">
+      <c r="I30" s="7">
         <v>0.7</v>
       </c>
-      <c r="J30">
+      <c r="J30" s="7">
         <v>2.9</v>
       </c>
-      <c r="K30">
+      <c r="K30" s="7">
         <v>3.4</v>
       </c>
-      <c r="L30">
+      <c r="L30" s="8">
         <v>83</v>
       </c>
-      <c r="M30">
+      <c r="M30" s="7">
         <v>115.9</v>
       </c>
-      <c r="N30">
+      <c r="N30" s="3">
         <v>0.39</v>
       </c>
-      <c r="O30">
+      <c r="O30" s="7">
         <v>6.1</v>
       </c>
-      <c r="P30">
+      <c r="P30" s="7">
         <v>3.4</v>
       </c>
-      <c r="Q30">
+      <c r="Q30" s="3">
         <v>0.56000000000000005</v>
       </c>
-      <c r="R30">
+      <c r="R30" s="8">
         <v>3857</v>
       </c>
-      <c r="S30">
+      <c r="S30" s="8">
         <v>231</v>
       </c>
-      <c r="T30">
+      <c r="T30" s="8">
         <v>584</v>
       </c>
-      <c r="U30">
+      <c r="U30" s="7">
         <v>24</v>
       </c>
     </row>
@@ -3585,52 +3588,52 @@
       <c r="E31">
         <v>140</v>
       </c>
-      <c r="F31">
+      <c r="F31" s="7">
         <v>8.3000000000000007</v>
       </c>
-      <c r="G31">
+      <c r="G31" s="7">
         <v>7.2</v>
       </c>
-      <c r="H31">
+      <c r="H31" s="3">
         <v>1.04</v>
       </c>
-      <c r="I31">
+      <c r="I31" s="7">
         <v>0.6</v>
       </c>
-      <c r="J31">
+      <c r="J31" s="7">
         <v>1.9</v>
       </c>
-      <c r="K31">
+      <c r="K31" s="7">
         <v>3.2</v>
       </c>
-      <c r="L31">
+      <c r="L31" s="8">
         <v>92</v>
       </c>
-      <c r="M31">
+      <c r="M31" s="7">
         <v>101.3</v>
       </c>
-      <c r="N31">
+      <c r="N31" s="3">
         <v>0.33</v>
       </c>
-      <c r="O31">
+      <c r="O31" s="7">
         <v>4.5999999999999996</v>
       </c>
-      <c r="P31">
+      <c r="P31" s="7">
         <v>2.5</v>
       </c>
-      <c r="Q31">
+      <c r="Q31" s="3">
         <v>0.45</v>
       </c>
-      <c r="R31">
+      <c r="R31" s="8">
         <v>3896</v>
       </c>
-      <c r="S31">
+      <c r="S31" s="8">
         <v>252</v>
       </c>
-      <c r="T31">
+      <c r="T31" s="8">
         <v>390</v>
       </c>
-      <c r="U31">
+      <c r="U31" s="7">
         <v>23.5</v>
       </c>
     </row>
@@ -3650,52 +3653,52 @@
       <c r="E32">
         <v>180</v>
       </c>
-      <c r="F32">
+      <c r="F32" s="7">
         <v>8.3000000000000007</v>
       </c>
-      <c r="G32">
+      <c r="G32" s="7">
         <v>7.2</v>
       </c>
-      <c r="H32">
+      <c r="H32" s="3">
         <v>1.06</v>
       </c>
-      <c r="I32">
+      <c r="I32" s="7">
         <v>0.8</v>
       </c>
-      <c r="J32">
+      <c r="J32" s="7">
         <v>2.2999999999999998</v>
       </c>
-      <c r="K32">
+      <c r="K32" s="7">
         <v>3.4</v>
       </c>
-      <c r="L32">
+      <c r="L32" s="8">
         <v>92</v>
       </c>
-      <c r="M32">
+      <c r="M32" s="7">
         <v>104.6</v>
       </c>
-      <c r="N32">
+      <c r="N32" s="3">
         <v>0.36</v>
       </c>
-      <c r="O32">
+      <c r="O32" s="7">
         <v>4.8</v>
       </c>
-      <c r="P32">
+      <c r="P32" s="7">
         <v>2.1</v>
       </c>
-      <c r="Q32">
+      <c r="Q32" s="3">
         <v>0.33</v>
       </c>
-      <c r="R32">
+      <c r="R32" s="8">
         <v>5319</v>
       </c>
-      <c r="S32">
+      <c r="S32" s="8">
         <v>269</v>
       </c>
-      <c r="T32">
+      <c r="T32" s="8">
         <v>276</v>
       </c>
-      <c r="U32">
+      <c r="U32" s="7">
         <v>30.3</v>
       </c>
     </row>

--- a/Data/2021_F013B4_CO_ISSWC/2021_F013B4_CO_ISSWC_SoilAnalysis.xlsx
+++ b/Data/2021_F013B4_CO_ISSWC/2021_F013B4_CO_ISSWC_SoilAnalysis.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28925"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\mnt\Data1\USDA-ALARC\GIS\PDI project\cottondata\Data\2021_F013B4_CO_ISSWC\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{322A8724-5378-4003-884C-0C31BA4427A5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5802F9FA-9B80-406E-887F-3ECBB440512E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="16320" yWindow="-28050" windowWidth="17910" windowHeight="25080" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-1665" yWindow="-28020" windowWidth="27270" windowHeight="17295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="SoilDJH" sheetId="5" r:id="rId1"/>
@@ -1055,9 +1055,6 @@
     <t>p01-1</t>
   </si>
   <si>
-    <t>2013d260EM38</t>
-  </si>
-  <si>
     <t>2015d118EM38</t>
   </si>
   <si>
@@ -1629,6 +1626,9 @@
   </si>
   <si>
     <t>2016-p16-1</t>
+  </si>
+  <si>
+    <t>2013d260EM38V</t>
   </si>
 </sst>
 </file>
@@ -2480,13 +2480,13 @@
         <v>296</v>
       </c>
       <c r="B1" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="C1" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="D1" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="E1" t="s">
         <v>0</v>
@@ -2497,7 +2497,7 @@
         <v>115</v>
       </c>
       <c r="B2" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="C2">
         <v>408706.2476</v>
@@ -2514,7 +2514,7 @@
         <v>116</v>
       </c>
       <c r="B3" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="C3">
         <v>408705.94109999901</v>
@@ -2531,7 +2531,7 @@
         <v>129</v>
       </c>
       <c r="B4" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="C4">
         <v>408699.85230000003</v>
@@ -2548,7 +2548,7 @@
         <v>130</v>
       </c>
       <c r="B5" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="C5">
         <v>408700.13030000002</v>
@@ -2565,7 +2565,7 @@
         <v>117</v>
       </c>
       <c r="B6" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="C6">
         <v>408705.62539999897</v>
@@ -2582,7 +2582,7 @@
         <v>118</v>
       </c>
       <c r="B7" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="C7">
         <v>408705.38500000001</v>
@@ -2599,7 +2599,7 @@
         <v>127</v>
       </c>
       <c r="B8" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="C8">
         <v>408699.26530000003</v>
@@ -2616,7 +2616,7 @@
         <v>128</v>
       </c>
       <c r="B9" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="C9">
         <v>408699.535299999</v>
@@ -2633,7 +2633,7 @@
         <v>119</v>
       </c>
       <c r="B10" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="C10">
         <v>408704.99829999899</v>
@@ -2650,7 +2650,7 @@
         <v>126</v>
       </c>
       <c r="B11" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="C11">
         <v>408698.93699999899</v>
@@ -2667,7 +2667,7 @@
         <v>121</v>
       </c>
       <c r="B12" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="C12">
         <v>408704.38349999901</v>
@@ -2684,7 +2684,7 @@
         <v>124</v>
       </c>
       <c r="B13" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="C13">
         <v>408698.26829999901</v>
@@ -2701,7 +2701,7 @@
         <v>99</v>
       </c>
       <c r="B14" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="C14">
         <v>408720.46580000001</v>
@@ -2718,7 +2718,7 @@
         <v>100</v>
       </c>
       <c r="B15" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="C15">
         <v>408720.19679999899</v>
@@ -2735,7 +2735,7 @@
         <v>113</v>
       </c>
       <c r="B16" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="C16">
         <v>408714.09700000001</v>
@@ -2752,7 +2752,7 @@
         <v>114</v>
       </c>
       <c r="B17" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="C17">
         <v>408714.40309999901</v>
@@ -2769,7 +2769,7 @@
         <v>101</v>
       </c>
       <c r="B18" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="C18">
         <v>408719.8885</v>
@@ -2786,7 +2786,7 @@
         <v>102</v>
       </c>
       <c r="B19" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="C19">
         <v>408719.60830000002</v>
@@ -2803,7 +2803,7 @@
         <v>111</v>
       </c>
       <c r="B20" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="C20">
         <v>408713.53340000001</v>
@@ -2820,7 +2820,7 @@
         <v>112</v>
       </c>
       <c r="B21" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="C21">
         <v>408713.790299999</v>
@@ -2837,7 +2837,7 @@
         <v>103</v>
       </c>
       <c r="B22" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="C22">
         <v>408719.22999999899</v>
@@ -2854,7 +2854,7 @@
         <v>110</v>
       </c>
       <c r="B23" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="C23">
         <v>408713.13880000002</v>
@@ -2871,7 +2871,7 @@
         <v>105</v>
       </c>
       <c r="B24" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="C24">
         <v>408718.61729999899</v>
@@ -2888,7 +2888,7 @@
         <v>108</v>
       </c>
       <c r="B25" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="C25">
         <v>408712.455599999</v>
@@ -2905,7 +2905,7 @@
         <v>83</v>
       </c>
       <c r="B26" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="C26">
         <v>408734.69020000001</v>
@@ -2922,7 +2922,7 @@
         <v>84</v>
       </c>
       <c r="B27" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="C27">
         <v>408734.44760000001</v>
@@ -2939,7 +2939,7 @@
         <v>97</v>
       </c>
       <c r="B28" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="C28">
         <v>408728.347899999</v>
@@ -2956,7 +2956,7 @@
         <v>98</v>
       </c>
       <c r="B29" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="C29">
         <v>408728.57990000001</v>
@@ -2973,7 +2973,7 @@
         <v>85</v>
       </c>
       <c r="B30" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="C30">
         <v>408734.16200000001</v>
@@ -2990,7 +2990,7 @@
         <v>86</v>
       </c>
       <c r="B31" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="C31">
         <v>408733.81439999898</v>
@@ -3007,7 +3007,7 @@
         <v>95</v>
       </c>
       <c r="B32" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="C32">
         <v>408727.74089999998</v>
@@ -3024,7 +3024,7 @@
         <v>96</v>
       </c>
       <c r="B33" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="C33">
         <v>408727.98920000001</v>
@@ -3041,7 +3041,7 @@
         <v>87</v>
       </c>
       <c r="B34" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="C34">
         <v>408733.443499999</v>
@@ -3058,7 +3058,7 @@
         <v>94</v>
       </c>
       <c r="B35" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="C35">
         <v>408727.3763</v>
@@ -3075,7 +3075,7 @@
         <v>89</v>
       </c>
       <c r="B36" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="C36">
         <v>408732.84250000003</v>
@@ -3092,7 +3092,7 @@
         <v>92</v>
       </c>
       <c r="B37" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="C37">
         <v>408726.75140000001</v>
@@ -3109,7 +3109,7 @@
         <v>67</v>
       </c>
       <c r="B38" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="C38">
         <v>408748.9094</v>
@@ -3126,7 +3126,7 @@
         <v>68</v>
       </c>
       <c r="B39" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="C39">
         <v>408748.6594</v>
@@ -3143,7 +3143,7 @@
         <v>81</v>
       </c>
       <c r="B40" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="C40">
         <v>408742.57679999899</v>
@@ -3160,7 +3160,7 @@
         <v>82</v>
       </c>
       <c r="B41" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="C41">
         <v>408742.84710000001</v>
@@ -3177,7 +3177,7 @@
         <v>69</v>
       </c>
       <c r="B42" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="C42">
         <v>408748.33390000003</v>
@@ -3194,7 +3194,7 @@
         <v>70</v>
       </c>
       <c r="B43" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="C43">
         <v>408747.98800000001</v>
@@ -3211,7 +3211,7 @@
         <v>79</v>
       </c>
       <c r="B44" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="C44">
         <v>408741.9215</v>
@@ -3228,7 +3228,7 @@
         <v>80</v>
       </c>
       <c r="B45" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="C45">
         <v>408742.204399999</v>
@@ -3245,7 +3245,7 @@
         <v>71</v>
       </c>
       <c r="B46" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="C46">
         <v>408747.652899999</v>
@@ -3262,7 +3262,7 @@
         <v>78</v>
       </c>
       <c r="B47" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="C47">
         <v>408741.583099999</v>
@@ -3279,7 +3279,7 @@
         <v>73</v>
       </c>
       <c r="B48" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="C48">
         <v>408747.01990000001</v>
@@ -3296,7 +3296,7 @@
         <v>76</v>
       </c>
       <c r="B49" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="C49">
         <v>408740.96580000001</v>
@@ -3313,7 +3313,7 @@
         <v>60</v>
       </c>
       <c r="B50" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="C50">
         <v>408760.11839999899</v>
@@ -3330,7 +3330,7 @@
         <v>58</v>
       </c>
       <c r="B51" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="C51">
         <v>408759.24219999899</v>
@@ -3347,7 +3347,7 @@
         <v>57</v>
       </c>
       <c r="B52" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="C52">
         <v>408758.807399999</v>
@@ -3364,7 +3364,7 @@
         <v>56</v>
       </c>
       <c r="B53" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="C53">
         <v>408758.367499999</v>
@@ -3381,7 +3381,7 @@
         <v>49</v>
       </c>
       <c r="B54" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="C54">
         <v>408788.581799999</v>
@@ -3398,7 +3398,7 @@
         <v>166</v>
       </c>
       <c r="B55" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="C55">
         <v>408793.35800000001</v>
@@ -3415,7 +3415,7 @@
         <v>51</v>
       </c>
       <c r="B56" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="C56">
         <v>408787.67560000002</v>
@@ -3432,7 +3432,7 @@
         <v>167</v>
       </c>
       <c r="B57" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="C57">
         <v>408792.866099999</v>
@@ -3449,7 +3449,7 @@
         <v>52</v>
       </c>
       <c r="B58" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="C58">
         <v>408787.222799999</v>
@@ -3466,7 +3466,7 @@
         <v>168</v>
       </c>
       <c r="B59" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="C59">
         <v>408792.38530000002</v>
@@ -3483,7 +3483,7 @@
         <v>53</v>
       </c>
       <c r="B60" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="C60">
         <v>408786.80749999901</v>
@@ -3500,7 +3500,7 @@
         <v>170</v>
       </c>
       <c r="B61" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="C61">
         <v>408791.43050000002</v>
@@ -3517,7 +3517,7 @@
         <v>48</v>
       </c>
       <c r="B62" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="C62">
         <v>408817.00829999999</v>
@@ -3534,7 +3534,7 @@
         <v>46</v>
       </c>
       <c r="B63" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="C63">
         <v>408816.12689999898</v>
@@ -3551,7 +3551,7 @@
         <v>45</v>
       </c>
       <c r="B64" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="C64">
         <v>408815.666399999</v>
@@ -3568,7 +3568,7 @@
         <v>44</v>
       </c>
       <c r="B65" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="C65">
         <v>408815.248499999</v>
@@ -3585,7 +3585,7 @@
         <v>37</v>
       </c>
       <c r="B66" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="C66">
         <v>408845.46089999902</v>
@@ -3602,7 +3602,7 @@
         <v>156</v>
       </c>
       <c r="B67" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="C67">
         <v>408850.18070000003</v>
@@ -3619,7 +3619,7 @@
         <v>39</v>
       </c>
       <c r="B68" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="C68">
         <v>408844.56319999899</v>
@@ -3636,7 +3636,7 @@
         <v>157</v>
       </c>
       <c r="B69" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="C69">
         <v>408849.70020000002</v>
@@ -3653,7 +3653,7 @@
         <v>40</v>
       </c>
       <c r="B70" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="C70">
         <v>408844.13500000001</v>
@@ -3670,7 +3670,7 @@
         <v>158</v>
       </c>
       <c r="B71" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="C71">
         <v>408849.219199999</v>
@@ -3687,7 +3687,7 @@
         <v>41</v>
       </c>
       <c r="B72" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="C72">
         <v>408843.68329999998</v>
@@ -3704,7 +3704,7 @@
         <v>160</v>
       </c>
       <c r="B73" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="C73">
         <v>408848.231299999</v>
@@ -3734,13 +3734,13 @@
         <v>296</v>
       </c>
       <c r="B1" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="C1" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="D1" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="E1" t="s">
         <v>0</v>
@@ -3751,7 +3751,7 @@
         <v>61</v>
       </c>
       <c r="B2" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="C2">
         <v>408702.95299999899</v>
@@ -3768,7 +3768,7 @@
         <v>62</v>
       </c>
       <c r="B3" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="C3">
         <v>408702.35950000002</v>
@@ -3785,7 +3785,7 @@
         <v>63</v>
       </c>
       <c r="B4" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="C4">
         <v>408701.76500000001</v>
@@ -3802,7 +3802,7 @@
         <v>64</v>
       </c>
       <c r="B5" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="C5">
         <v>408701.14669999899</v>
@@ -3819,7 +3819,7 @@
         <v>57</v>
       </c>
       <c r="B6" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="C6">
         <v>408717.2047</v>
@@ -3836,7 +3836,7 @@
         <v>58</v>
       </c>
       <c r="B7" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="C7">
         <v>408716.59240000002</v>
@@ -3853,7 +3853,7 @@
         <v>59</v>
       </c>
       <c r="B8" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="C8">
         <v>408715.98029999901</v>
@@ -3870,7 +3870,7 @@
         <v>60</v>
       </c>
       <c r="B9" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="C9">
         <v>408715.38030000002</v>
@@ -3887,7 +3887,7 @@
         <v>53</v>
       </c>
       <c r="B10" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="C10">
         <v>408731.41739999899</v>
@@ -3904,7 +3904,7 @@
         <v>54</v>
       </c>
       <c r="B11" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="C11">
         <v>408730.80660000001</v>
@@ -3921,7 +3921,7 @@
         <v>55</v>
       </c>
       <c r="B12" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="C12">
         <v>408730.19</v>
@@ -3938,7 +3938,7 @@
         <v>56</v>
       </c>
       <c r="B13" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="C13">
         <v>408729.61050000001</v>
@@ -3955,7 +3955,7 @@
         <v>49</v>
       </c>
       <c r="B14" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="C14">
         <v>408745.63719999901</v>
@@ -3972,7 +3972,7 @@
         <v>50</v>
       </c>
       <c r="B15" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="C15">
         <v>408745.02610000002</v>
@@ -3989,7 +3989,7 @@
         <v>51</v>
       </c>
       <c r="B16" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="C16">
         <v>408744.41419999901</v>
@@ -4006,7 +4006,7 @@
         <v>52</v>
       </c>
       <c r="B17" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="C17">
         <v>408743.81449999899</v>
@@ -4023,7 +4023,7 @@
         <v>45</v>
       </c>
       <c r="B18" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="C18">
         <v>408759.7758</v>
@@ -4040,7 +4040,7 @@
         <v>46</v>
       </c>
       <c r="B19" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="C19">
         <v>408759.1692</v>
@@ -4057,7 +4057,7 @@
         <v>47</v>
       </c>
       <c r="B20" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="C20">
         <v>408758.57179999899</v>
@@ -4074,7 +4074,7 @@
         <v>48</v>
       </c>
       <c r="B21" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="C21">
         <v>408757.959299999</v>
@@ -4091,7 +4091,7 @@
         <v>41</v>
       </c>
       <c r="B22" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="C22">
         <v>408773.99790000002</v>
@@ -4108,7 +4108,7 @@
         <v>42</v>
       </c>
       <c r="B23" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="C23">
         <v>408773.39649999898</v>
@@ -4125,7 +4125,7 @@
         <v>43</v>
       </c>
       <c r="B24" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="C24">
         <v>408772.784099999</v>
@@ -4142,7 +4142,7 @@
         <v>44</v>
       </c>
       <c r="B25" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="C25">
         <v>408772.17050000001</v>
@@ -4159,7 +4159,7 @@
         <v>37</v>
       </c>
       <c r="B26" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="C26">
         <v>408788.22350000002</v>
@@ -4176,7 +4176,7 @@
         <v>38</v>
       </c>
       <c r="B27" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="C27">
         <v>408787.60700000002</v>
@@ -4193,7 +4193,7 @@
         <v>39</v>
       </c>
       <c r="B28" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="C28">
         <v>408787.00040000002</v>
@@ -4210,7 +4210,7 @@
         <v>40</v>
       </c>
       <c r="B29" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="C29">
         <v>408786.40159999899</v>
@@ -4227,7 +4227,7 @@
         <v>33</v>
       </c>
       <c r="B30" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="C30">
         <v>408802.449499999</v>
@@ -4244,7 +4244,7 @@
         <v>34</v>
       </c>
       <c r="B31" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="C31">
         <v>408801.83819999901</v>
@@ -4261,7 +4261,7 @@
         <v>35</v>
       </c>
       <c r="B32" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="C32">
         <v>408801.21379999898</v>
@@ -4278,7 +4278,7 @@
         <v>36</v>
       </c>
       <c r="B33" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="C33">
         <v>408800.62819999899</v>
@@ -4295,7 +4295,7 @@
         <v>29</v>
       </c>
       <c r="B34" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="C34">
         <v>408816.59179999901</v>
@@ -4312,7 +4312,7 @@
         <v>30</v>
       </c>
       <c r="B35" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="C35">
         <v>408815.986199999</v>
@@ -4329,7 +4329,7 @@
         <v>31</v>
       </c>
       <c r="B36" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="C36">
         <v>408815.39</v>
@@ -4346,7 +4346,7 @@
         <v>32</v>
       </c>
       <c r="B37" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="C37">
         <v>408814.777</v>
@@ -4363,7 +4363,7 @@
         <v>25</v>
       </c>
       <c r="B38" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="C38">
         <v>408830.81489999901</v>
@@ -4380,7 +4380,7 @@
         <v>26</v>
       </c>
       <c r="B39" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="C39">
         <v>408830.206899999</v>
@@ -4397,7 +4397,7 @@
         <v>27</v>
       </c>
       <c r="B40" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="C40">
         <v>408829.59519999899</v>
@@ -4414,7 +4414,7 @@
         <v>28</v>
       </c>
       <c r="B41" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="C41">
         <v>408828.99920000002</v>
@@ -4431,7 +4431,7 @@
         <v>21</v>
       </c>
       <c r="B42" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="C42">
         <v>408845.03460000001</v>
@@ -4448,7 +4448,7 @@
         <v>22</v>
       </c>
       <c r="B43" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="C43">
         <v>408844.4375</v>
@@ -4465,7 +4465,7 @@
         <v>23</v>
       </c>
       <c r="B44" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="C44">
         <v>408843.829399999</v>
@@ -4482,7 +4482,7 @@
         <v>24</v>
       </c>
       <c r="B45" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="C45">
         <v>408843.20490000001</v>
@@ -4499,7 +4499,7 @@
         <v>17</v>
       </c>
       <c r="B46" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="C46">
         <v>408859.25290000002</v>
@@ -4516,7 +4516,7 @@
         <v>18</v>
       </c>
       <c r="B47" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="C47">
         <v>408858.64659999899</v>
@@ -4533,7 +4533,7 @@
         <v>19</v>
       </c>
       <c r="B48" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="C48">
         <v>408858.0344</v>
@@ -4550,7 +4550,7 @@
         <v>20</v>
       </c>
       <c r="B49" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="C49">
         <v>408857.44079999899</v>
@@ -4580,211 +4580,211 @@
         <v>295</v>
       </c>
       <c r="C1" t="s">
+        <v>530</v>
+      </c>
+      <c r="D1" t="s">
         <v>339</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
         <v>340</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
         <v>341</v>
       </c>
-      <c r="F1" t="s">
+      <c r="G1" t="s">
         <v>342</v>
       </c>
-      <c r="G1" t="s">
+      <c r="H1" t="s">
         <v>343</v>
       </c>
-      <c r="H1" t="s">
+      <c r="I1" t="s">
         <v>344</v>
       </c>
-      <c r="I1" t="s">
+      <c r="J1" t="s">
         <v>345</v>
       </c>
-      <c r="J1" t="s">
+      <c r="K1" t="s">
         <v>346</v>
       </c>
-      <c r="K1" t="s">
+      <c r="L1" t="s">
         <v>347</v>
       </c>
-      <c r="L1" t="s">
+      <c r="M1" t="s">
         <v>348</v>
       </c>
-      <c r="M1" t="s">
+      <c r="N1" t="s">
         <v>349</v>
       </c>
-      <c r="N1" t="s">
+      <c r="O1" t="s">
         <v>350</v>
       </c>
-      <c r="O1" t="s">
+      <c r="P1" t="s">
         <v>351</v>
       </c>
-      <c r="P1" t="s">
+      <c r="Q1" t="s">
         <v>352</v>
       </c>
-      <c r="Q1" t="s">
+      <c r="R1" t="s">
         <v>353</v>
       </c>
-      <c r="R1" t="s">
+      <c r="S1" t="s">
         <v>354</v>
       </c>
-      <c r="S1" t="s">
+      <c r="T1" t="s">
         <v>355</v>
       </c>
-      <c r="T1" t="s">
+      <c r="U1" t="s">
         <v>356</v>
       </c>
-      <c r="U1" t="s">
+      <c r="V1" t="s">
         <v>357</v>
       </c>
-      <c r="V1" t="s">
+      <c r="W1" t="s">
         <v>358</v>
       </c>
-      <c r="W1" t="s">
+      <c r="X1" t="s">
         <v>359</v>
       </c>
-      <c r="X1" t="s">
+      <c r="Y1" t="s">
         <v>360</v>
       </c>
-      <c r="Y1" t="s">
+      <c r="Z1" t="s">
         <v>361</v>
       </c>
-      <c r="Z1" t="s">
+      <c r="AA1" t="s">
         <v>362</v>
       </c>
-      <c r="AA1" t="s">
+      <c r="AB1" t="s">
         <v>363</v>
       </c>
-      <c r="AB1" t="s">
+      <c r="AC1" t="s">
         <v>364</v>
       </c>
-      <c r="AC1" t="s">
+      <c r="AD1" t="s">
         <v>365</v>
       </c>
-      <c r="AD1" t="s">
+      <c r="AE1" t="s">
         <v>366</v>
       </c>
-      <c r="AE1" t="s">
+      <c r="AF1" t="s">
         <v>367</v>
       </c>
-      <c r="AF1" t="s">
+      <c r="AG1" t="s">
         <v>368</v>
       </c>
-      <c r="AG1" t="s">
+      <c r="AH1" t="s">
         <v>369</v>
       </c>
-      <c r="AH1" t="s">
+      <c r="AI1" t="s">
         <v>370</v>
       </c>
-      <c r="AI1" t="s">
+      <c r="AJ1" t="s">
         <v>371</v>
       </c>
-      <c r="AJ1" t="s">
+      <c r="AK1" t="s">
         <v>372</v>
       </c>
-      <c r="AK1" t="s">
+      <c r="AL1" t="s">
         <v>373</v>
       </c>
-      <c r="AL1" t="s">
+      <c r="AM1" t="s">
         <v>374</v>
       </c>
-      <c r="AM1" t="s">
+      <c r="AN1" t="s">
         <v>375</v>
       </c>
-      <c r="AN1" t="s">
+      <c r="AO1" t="s">
         <v>376</v>
       </c>
-      <c r="AO1" t="s">
+      <c r="AP1" t="s">
         <v>377</v>
       </c>
-      <c r="AP1" t="s">
+      <c r="AQ1" t="s">
         <v>378</v>
       </c>
-      <c r="AQ1" t="s">
+      <c r="AR1" t="s">
         <v>379</v>
       </c>
-      <c r="AR1" t="s">
+      <c r="AS1" t="s">
         <v>380</v>
       </c>
-      <c r="AS1" t="s">
+      <c r="AT1" t="s">
         <v>381</v>
       </c>
-      <c r="AT1" t="s">
+      <c r="AU1" t="s">
         <v>382</v>
       </c>
-      <c r="AU1" t="s">
+      <c r="AV1" t="s">
         <v>383</v>
       </c>
-      <c r="AV1" t="s">
+      <c r="AW1" t="s">
         <v>384</v>
       </c>
-      <c r="AW1" t="s">
+      <c r="AX1" t="s">
         <v>385</v>
       </c>
-      <c r="AX1" t="s">
+      <c r="AY1" t="s">
         <v>386</v>
       </c>
-      <c r="AY1" t="s">
+      <c r="AZ1" t="s">
         <v>387</v>
       </c>
-      <c r="AZ1" t="s">
+      <c r="BA1" t="s">
         <v>388</v>
       </c>
-      <c r="BA1" t="s">
+      <c r="BB1" t="s">
         <v>389</v>
       </c>
-      <c r="BB1" t="s">
+      <c r="BC1" t="s">
         <v>390</v>
       </c>
-      <c r="BC1" t="s">
+      <c r="BD1" t="s">
         <v>391</v>
       </c>
-      <c r="BD1" t="s">
+      <c r="BE1" t="s">
         <v>392</v>
       </c>
-      <c r="BE1" t="s">
+      <c r="BF1" t="s">
         <v>393</v>
       </c>
-      <c r="BF1" t="s">
+      <c r="BG1" t="s">
         <v>394</v>
       </c>
-      <c r="BG1" t="s">
+      <c r="BH1" t="s">
         <v>395</v>
       </c>
-      <c r="BH1" t="s">
+      <c r="BI1" t="s">
         <v>396</v>
       </c>
-      <c r="BI1" t="s">
+      <c r="BJ1" t="s">
         <v>397</v>
       </c>
-      <c r="BJ1" t="s">
+      <c r="BK1" t="s">
         <v>398</v>
       </c>
-      <c r="BK1" t="s">
+      <c r="BL1" t="s">
         <v>399</v>
       </c>
-      <c r="BL1" t="s">
+      <c r="BM1" t="s">
         <v>400</v>
       </c>
-      <c r="BM1" t="s">
+      <c r="BN1" t="s">
         <v>401</v>
       </c>
-      <c r="BN1" t="s">
+      <c r="BO1" t="s">
         <v>402</v>
       </c>
-      <c r="BO1" t="s">
+      <c r="BP1" t="s">
         <v>403</v>
       </c>
-      <c r="BP1" t="s">
+      <c r="BQ1" t="s">
         <v>404</v>
       </c>
-      <c r="BQ1" t="s">
+      <c r="BR1" t="s">
         <v>405</v>
       </c>
-      <c r="BR1" t="s">
+      <c r="BS1" t="s">
         <v>406</v>
-      </c>
-      <c r="BS1" t="s">
-        <v>407</v>
       </c>
     </row>
     <row r="2" spans="1:71" x14ac:dyDescent="0.25">
@@ -65513,211 +65513,211 @@
         <v>0</v>
       </c>
       <c r="C1" t="s">
+        <v>530</v>
+      </c>
+      <c r="D1" t="s">
         <v>339</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
         <v>340</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
         <v>341</v>
       </c>
-      <c r="F1" t="s">
+      <c r="G1" t="s">
         <v>342</v>
       </c>
-      <c r="G1" t="s">
+      <c r="H1" t="s">
         <v>343</v>
       </c>
-      <c r="H1" t="s">
+      <c r="I1" t="s">
         <v>344</v>
       </c>
-      <c r="I1" t="s">
+      <c r="J1" t="s">
         <v>345</v>
       </c>
-      <c r="J1" t="s">
+      <c r="K1" t="s">
         <v>346</v>
       </c>
-      <c r="K1" t="s">
+      <c r="L1" t="s">
         <v>347</v>
       </c>
-      <c r="L1" t="s">
+      <c r="M1" t="s">
         <v>348</v>
       </c>
-      <c r="M1" t="s">
+      <c r="N1" t="s">
         <v>349</v>
       </c>
-      <c r="N1" t="s">
+      <c r="O1" t="s">
         <v>350</v>
       </c>
-      <c r="O1" t="s">
+      <c r="P1" t="s">
         <v>351</v>
       </c>
-      <c r="P1" t="s">
+      <c r="Q1" t="s">
         <v>352</v>
       </c>
-      <c r="Q1" t="s">
+      <c r="R1" t="s">
         <v>353</v>
       </c>
-      <c r="R1" t="s">
+      <c r="S1" t="s">
         <v>354</v>
       </c>
-      <c r="S1" t="s">
+      <c r="T1" t="s">
         <v>355</v>
       </c>
-      <c r="T1" t="s">
+      <c r="U1" t="s">
         <v>356</v>
       </c>
-      <c r="U1" t="s">
+      <c r="V1" t="s">
         <v>357</v>
       </c>
-      <c r="V1" t="s">
+      <c r="W1" t="s">
         <v>358</v>
       </c>
-      <c r="W1" t="s">
+      <c r="X1" t="s">
         <v>359</v>
       </c>
-      <c r="X1" t="s">
+      <c r="Y1" t="s">
         <v>360</v>
       </c>
-      <c r="Y1" t="s">
+      <c r="Z1" t="s">
         <v>361</v>
       </c>
-      <c r="Z1" t="s">
+      <c r="AA1" t="s">
         <v>362</v>
       </c>
-      <c r="AA1" t="s">
+      <c r="AB1" t="s">
         <v>363</v>
       </c>
-      <c r="AB1" t="s">
+      <c r="AC1" t="s">
         <v>364</v>
       </c>
-      <c r="AC1" t="s">
+      <c r="AD1" t="s">
         <v>365</v>
       </c>
-      <c r="AD1" t="s">
+      <c r="AE1" t="s">
         <v>366</v>
       </c>
-      <c r="AE1" t="s">
+      <c r="AF1" t="s">
         <v>367</v>
       </c>
-      <c r="AF1" t="s">
+      <c r="AG1" t="s">
         <v>368</v>
       </c>
-      <c r="AG1" t="s">
+      <c r="AH1" t="s">
         <v>369</v>
       </c>
-      <c r="AH1" t="s">
+      <c r="AI1" t="s">
         <v>370</v>
       </c>
-      <c r="AI1" t="s">
+      <c r="AJ1" t="s">
         <v>371</v>
       </c>
-      <c r="AJ1" t="s">
+      <c r="AK1" t="s">
         <v>372</v>
       </c>
-      <c r="AK1" t="s">
+      <c r="AL1" t="s">
         <v>373</v>
       </c>
-      <c r="AL1" t="s">
+      <c r="AM1" t="s">
         <v>374</v>
       </c>
-      <c r="AM1" t="s">
+      <c r="AN1" t="s">
         <v>375</v>
       </c>
-      <c r="AN1" t="s">
+      <c r="AO1" t="s">
         <v>376</v>
       </c>
-      <c r="AO1" t="s">
+      <c r="AP1" t="s">
         <v>377</v>
       </c>
-      <c r="AP1" t="s">
+      <c r="AQ1" t="s">
         <v>378</v>
       </c>
-      <c r="AQ1" t="s">
+      <c r="AR1" t="s">
         <v>379</v>
       </c>
-      <c r="AR1" t="s">
+      <c r="AS1" t="s">
         <v>380</v>
       </c>
-      <c r="AS1" t="s">
+      <c r="AT1" t="s">
         <v>381</v>
       </c>
-      <c r="AT1" t="s">
+      <c r="AU1" t="s">
         <v>382</v>
       </c>
-      <c r="AU1" t="s">
+      <c r="AV1" t="s">
         <v>383</v>
       </c>
-      <c r="AV1" t="s">
+      <c r="AW1" t="s">
         <v>384</v>
       </c>
-      <c r="AW1" t="s">
+      <c r="AX1" t="s">
         <v>385</v>
       </c>
-      <c r="AX1" t="s">
+      <c r="AY1" t="s">
         <v>386</v>
       </c>
-      <c r="AY1" t="s">
+      <c r="AZ1" t="s">
         <v>387</v>
       </c>
-      <c r="AZ1" t="s">
+      <c r="BA1" t="s">
         <v>388</v>
       </c>
-      <c r="BA1" t="s">
+      <c r="BB1" t="s">
         <v>389</v>
       </c>
-      <c r="BB1" t="s">
+      <c r="BC1" t="s">
         <v>390</v>
       </c>
-      <c r="BC1" t="s">
+      <c r="BD1" t="s">
         <v>391</v>
       </c>
-      <c r="BD1" t="s">
+      <c r="BE1" t="s">
         <v>392</v>
       </c>
-      <c r="BE1" t="s">
+      <c r="BF1" t="s">
         <v>393</v>
       </c>
-      <c r="BF1" t="s">
+      <c r="BG1" t="s">
         <v>394</v>
       </c>
-      <c r="BG1" t="s">
+      <c r="BH1" t="s">
         <v>395</v>
       </c>
-      <c r="BH1" t="s">
+      <c r="BI1" t="s">
         <v>396</v>
       </c>
-      <c r="BI1" t="s">
+      <c r="BJ1" t="s">
         <v>397</v>
       </c>
-      <c r="BJ1" t="s">
+      <c r="BK1" t="s">
         <v>398</v>
       </c>
-      <c r="BK1" t="s">
+      <c r="BL1" t="s">
         <v>399</v>
       </c>
-      <c r="BL1" t="s">
+      <c r="BM1" t="s">
         <v>400</v>
       </c>
-      <c r="BM1" t="s">
+      <c r="BN1" t="s">
         <v>401</v>
       </c>
-      <c r="BN1" t="s">
+      <c r="BO1" t="s">
         <v>402</v>
       </c>
-      <c r="BO1" t="s">
+      <c r="BP1" t="s">
         <v>403</v>
       </c>
-      <c r="BP1" t="s">
+      <c r="BQ1" t="s">
         <v>404</v>
       </c>
-      <c r="BQ1" t="s">
+      <c r="BR1" t="s">
         <v>405</v>
       </c>
-      <c r="BR1" t="s">
+      <c r="BS1" t="s">
         <v>406</v>
-      </c>
-      <c r="BS1" t="s">
-        <v>407</v>
       </c>
     </row>
     <row r="2" spans="1:71" x14ac:dyDescent="0.25">

--- a/Data/2021_F013B4_CO_ISSWC/2021_F013B4_CO_ISSWC_SoilAnalysis.xlsx
+++ b/Data/2021_F013B4_CO_ISSWC/2021_F013B4_CO_ISSWC_SoilAnalysis.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\mnt\Data1\USDA-ALARC\GIS\PDI project\cottondata\Data\2021_F013B4_CO_ISSWC\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6ABC6E6A-3020-4516-A641-C26613CEFD51}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{143D8FB9-6AA8-4810-8E6F-EB4CAFDB932E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-1425" yWindow="-24525" windowWidth="17775" windowHeight="24285" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-1815" yWindow="-26070" windowWidth="16335" windowHeight="23370" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="SoilDJH" sheetId="5" r:id="rId1"/>
@@ -1055,12 +1055,6 @@
     <t>p01-1</t>
   </si>
   <si>
-    <t>2015d118EM38</t>
-  </si>
-  <si>
-    <t>2015d119EM38</t>
-  </si>
-  <si>
     <t>SLSND015</t>
   </si>
   <si>
@@ -1629,6 +1623,12 @@
   </si>
   <si>
     <t>2013d260EM38V</t>
+  </si>
+  <si>
+    <t>2015d118EM38V</t>
+  </si>
+  <si>
+    <t>2015d119EM38V</t>
   </si>
 </sst>
 </file>
@@ -2480,13 +2480,13 @@
         <v>296</v>
       </c>
       <c r="B1" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="C1" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="D1" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="E1" t="s">
         <v>0</v>
@@ -2497,7 +2497,7 @@
         <v>115</v>
       </c>
       <c r="B2" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
       <c r="C2">
         <v>408706.2476</v>
@@ -2514,7 +2514,7 @@
         <v>116</v>
       </c>
       <c r="B3" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="C3">
         <v>408705.94109999901</v>
@@ -2531,7 +2531,7 @@
         <v>129</v>
       </c>
       <c r="B4" t="s">
-        <v>476</v>
+        <v>474</v>
       </c>
       <c r="C4">
         <v>408699.85230000003</v>
@@ -2548,7 +2548,7 @@
         <v>130</v>
       </c>
       <c r="B5" t="s">
-        <v>475</v>
+        <v>473</v>
       </c>
       <c r="C5">
         <v>408700.13030000002</v>
@@ -2565,7 +2565,7 @@
         <v>117</v>
       </c>
       <c r="B6" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
       <c r="C6">
         <v>408705.62539999897</v>
@@ -2582,7 +2582,7 @@
         <v>118</v>
       </c>
       <c r="B7" t="s">
-        <v>473</v>
+        <v>471</v>
       </c>
       <c r="C7">
         <v>408705.38500000001</v>
@@ -2599,7 +2599,7 @@
         <v>127</v>
       </c>
       <c r="B8" t="s">
-        <v>472</v>
+        <v>470</v>
       </c>
       <c r="C8">
         <v>408699.26530000003</v>
@@ -2616,7 +2616,7 @@
         <v>128</v>
       </c>
       <c r="B9" t="s">
-        <v>471</v>
+        <v>469</v>
       </c>
       <c r="C9">
         <v>408699.535299999</v>
@@ -2633,7 +2633,7 @@
         <v>119</v>
       </c>
       <c r="B10" t="s">
-        <v>470</v>
+        <v>468</v>
       </c>
       <c r="C10">
         <v>408704.99829999899</v>
@@ -2650,7 +2650,7 @@
         <v>126</v>
       </c>
       <c r="B11" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="C11">
         <v>408698.93699999899</v>
@@ -2667,7 +2667,7 @@
         <v>121</v>
       </c>
       <c r="B12" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="C12">
         <v>408704.38349999901</v>
@@ -2684,7 +2684,7 @@
         <v>124</v>
       </c>
       <c r="B13" t="s">
-        <v>467</v>
+        <v>465</v>
       </c>
       <c r="C13">
         <v>408698.26829999901</v>
@@ -2701,7 +2701,7 @@
         <v>99</v>
       </c>
       <c r="B14" t="s">
-        <v>466</v>
+        <v>464</v>
       </c>
       <c r="C14">
         <v>408720.46580000001</v>
@@ -2718,7 +2718,7 @@
         <v>100</v>
       </c>
       <c r="B15" t="s">
-        <v>465</v>
+        <v>463</v>
       </c>
       <c r="C15">
         <v>408720.19679999899</v>
@@ -2735,7 +2735,7 @@
         <v>113</v>
       </c>
       <c r="B16" t="s">
-        <v>464</v>
+        <v>462</v>
       </c>
       <c r="C16">
         <v>408714.09700000001</v>
@@ -2752,7 +2752,7 @@
         <v>114</v>
       </c>
       <c r="B17" t="s">
-        <v>463</v>
+        <v>461</v>
       </c>
       <c r="C17">
         <v>408714.40309999901</v>
@@ -2769,7 +2769,7 @@
         <v>101</v>
       </c>
       <c r="B18" t="s">
-        <v>462</v>
+        <v>460</v>
       </c>
       <c r="C18">
         <v>408719.8885</v>
@@ -2786,7 +2786,7 @@
         <v>102</v>
       </c>
       <c r="B19" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="C19">
         <v>408719.60830000002</v>
@@ -2803,7 +2803,7 @@
         <v>111</v>
       </c>
       <c r="B20" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="C20">
         <v>408713.53340000001</v>
@@ -2820,7 +2820,7 @@
         <v>112</v>
       </c>
       <c r="B21" t="s">
-        <v>459</v>
+        <v>457</v>
       </c>
       <c r="C21">
         <v>408713.790299999</v>
@@ -2837,7 +2837,7 @@
         <v>103</v>
       </c>
       <c r="B22" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
       <c r="C22">
         <v>408719.22999999899</v>
@@ -2854,7 +2854,7 @@
         <v>110</v>
       </c>
       <c r="B23" t="s">
-        <v>457</v>
+        <v>455</v>
       </c>
       <c r="C23">
         <v>408713.13880000002</v>
@@ -2871,7 +2871,7 @@
         <v>105</v>
       </c>
       <c r="B24" t="s">
-        <v>456</v>
+        <v>454</v>
       </c>
       <c r="C24">
         <v>408718.61729999899</v>
@@ -2888,7 +2888,7 @@
         <v>108</v>
       </c>
       <c r="B25" t="s">
-        <v>455</v>
+        <v>453</v>
       </c>
       <c r="C25">
         <v>408712.455599999</v>
@@ -2905,7 +2905,7 @@
         <v>83</v>
       </c>
       <c r="B26" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="C26">
         <v>408734.69020000001</v>
@@ -2922,7 +2922,7 @@
         <v>84</v>
       </c>
       <c r="B27" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="C27">
         <v>408734.44760000001</v>
@@ -2939,7 +2939,7 @@
         <v>97</v>
       </c>
       <c r="B28" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="C28">
         <v>408728.347899999</v>
@@ -2956,7 +2956,7 @@
         <v>98</v>
       </c>
       <c r="B29" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
       <c r="C29">
         <v>408728.57990000001</v>
@@ -2973,7 +2973,7 @@
         <v>85</v>
       </c>
       <c r="B30" t="s">
-        <v>450</v>
+        <v>448</v>
       </c>
       <c r="C30">
         <v>408734.16200000001</v>
@@ -2990,7 +2990,7 @@
         <v>86</v>
       </c>
       <c r="B31" t="s">
-        <v>449</v>
+        <v>447</v>
       </c>
       <c r="C31">
         <v>408733.81439999898</v>
@@ -3007,7 +3007,7 @@
         <v>95</v>
       </c>
       <c r="B32" t="s">
-        <v>448</v>
+        <v>446</v>
       </c>
       <c r="C32">
         <v>408727.74089999998</v>
@@ -3024,7 +3024,7 @@
         <v>96</v>
       </c>
       <c r="B33" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="C33">
         <v>408727.98920000001</v>
@@ -3041,7 +3041,7 @@
         <v>87</v>
       </c>
       <c r="B34" t="s">
-        <v>446</v>
+        <v>444</v>
       </c>
       <c r="C34">
         <v>408733.443499999</v>
@@ -3058,7 +3058,7 @@
         <v>94</v>
       </c>
       <c r="B35" t="s">
-        <v>445</v>
+        <v>443</v>
       </c>
       <c r="C35">
         <v>408727.3763</v>
@@ -3075,7 +3075,7 @@
         <v>89</v>
       </c>
       <c r="B36" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
       <c r="C36">
         <v>408732.84250000003</v>
@@ -3092,7 +3092,7 @@
         <v>92</v>
       </c>
       <c r="B37" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
       <c r="C37">
         <v>408726.75140000001</v>
@@ -3109,7 +3109,7 @@
         <v>67</v>
       </c>
       <c r="B38" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="C38">
         <v>408748.9094</v>
@@ -3126,7 +3126,7 @@
         <v>68</v>
       </c>
       <c r="B39" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
       <c r="C39">
         <v>408748.6594</v>
@@ -3143,7 +3143,7 @@
         <v>81</v>
       </c>
       <c r="B40" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="C40">
         <v>408742.57679999899</v>
@@ -3160,7 +3160,7 @@
         <v>82</v>
       </c>
       <c r="B41" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
       <c r="C41">
         <v>408742.84710000001</v>
@@ -3177,7 +3177,7 @@
         <v>69</v>
       </c>
       <c r="B42" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="C42">
         <v>408748.33390000003</v>
@@ -3194,7 +3194,7 @@
         <v>70</v>
       </c>
       <c r="B43" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="C43">
         <v>408747.98800000001</v>
@@ -3211,7 +3211,7 @@
         <v>79</v>
       </c>
       <c r="B44" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="C44">
         <v>408741.9215</v>
@@ -3228,7 +3228,7 @@
         <v>80</v>
       </c>
       <c r="B45" t="s">
-        <v>435</v>
+        <v>433</v>
       </c>
       <c r="C45">
         <v>408742.204399999</v>
@@ -3245,7 +3245,7 @@
         <v>71</v>
       </c>
       <c r="B46" t="s">
-        <v>434</v>
+        <v>432</v>
       </c>
       <c r="C46">
         <v>408747.652899999</v>
@@ -3262,7 +3262,7 @@
         <v>78</v>
       </c>
       <c r="B47" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="C47">
         <v>408741.583099999</v>
@@ -3279,7 +3279,7 @@
         <v>73</v>
       </c>
       <c r="B48" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="C48">
         <v>408747.01990000001</v>
@@ -3296,7 +3296,7 @@
         <v>76</v>
       </c>
       <c r="B49" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="C49">
         <v>408740.96580000001</v>
@@ -3313,7 +3313,7 @@
         <v>60</v>
       </c>
       <c r="B50" t="s">
-        <v>430</v>
+        <v>428</v>
       </c>
       <c r="C50">
         <v>408760.11839999899</v>
@@ -3330,7 +3330,7 @@
         <v>58</v>
       </c>
       <c r="B51" t="s">
-        <v>429</v>
+        <v>427</v>
       </c>
       <c r="C51">
         <v>408759.24219999899</v>
@@ -3347,7 +3347,7 @@
         <v>57</v>
       </c>
       <c r="B52" t="s">
-        <v>428</v>
+        <v>426</v>
       </c>
       <c r="C52">
         <v>408758.807399999</v>
@@ -3364,7 +3364,7 @@
         <v>56</v>
       </c>
       <c r="B53" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="C53">
         <v>408758.367499999</v>
@@ -3381,7 +3381,7 @@
         <v>49</v>
       </c>
       <c r="B54" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="C54">
         <v>408788.581799999</v>
@@ -3398,7 +3398,7 @@
         <v>166</v>
       </c>
       <c r="B55" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="C55">
         <v>408793.35800000001</v>
@@ -3415,7 +3415,7 @@
         <v>51</v>
       </c>
       <c r="B56" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="C56">
         <v>408787.67560000002</v>
@@ -3432,7 +3432,7 @@
         <v>167</v>
       </c>
       <c r="B57" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="C57">
         <v>408792.866099999</v>
@@ -3449,7 +3449,7 @@
         <v>52</v>
       </c>
       <c r="B58" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="C58">
         <v>408787.222799999</v>
@@ -3466,7 +3466,7 @@
         <v>168</v>
       </c>
       <c r="B59" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="C59">
         <v>408792.38530000002</v>
@@ -3483,7 +3483,7 @@
         <v>53</v>
       </c>
       <c r="B60" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="C60">
         <v>408786.80749999901</v>
@@ -3500,7 +3500,7 @@
         <v>170</v>
       </c>
       <c r="B61" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="C61">
         <v>408791.43050000002</v>
@@ -3517,7 +3517,7 @@
         <v>48</v>
       </c>
       <c r="B62" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="C62">
         <v>408817.00829999999</v>
@@ -3534,7 +3534,7 @@
         <v>46</v>
       </c>
       <c r="B63" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="C63">
         <v>408816.12689999898</v>
@@ -3551,7 +3551,7 @@
         <v>45</v>
       </c>
       <c r="B64" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="C64">
         <v>408815.666399999</v>
@@ -3568,7 +3568,7 @@
         <v>44</v>
       </c>
       <c r="B65" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
       <c r="C65">
         <v>408815.248499999</v>
@@ -3585,7 +3585,7 @@
         <v>37</v>
       </c>
       <c r="B66" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="C66">
         <v>408845.46089999902</v>
@@ -3602,7 +3602,7 @@
         <v>156</v>
       </c>
       <c r="B67" t="s">
-        <v>413</v>
+        <v>411</v>
       </c>
       <c r="C67">
         <v>408850.18070000003</v>
@@ -3619,7 +3619,7 @@
         <v>39</v>
       </c>
       <c r="B68" t="s">
-        <v>412</v>
+        <v>410</v>
       </c>
       <c r="C68">
         <v>408844.56319999899</v>
@@ -3636,7 +3636,7 @@
         <v>157</v>
       </c>
       <c r="B69" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
       <c r="C69">
         <v>408849.70020000002</v>
@@ -3653,7 +3653,7 @@
         <v>40</v>
       </c>
       <c r="B70" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="C70">
         <v>408844.13500000001</v>
@@ -3670,7 +3670,7 @@
         <v>158</v>
       </c>
       <c r="B71" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="C71">
         <v>408849.219199999</v>
@@ -3687,7 +3687,7 @@
         <v>41</v>
       </c>
       <c r="B72" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="C72">
         <v>408843.68329999998</v>
@@ -3704,7 +3704,7 @@
         <v>160</v>
       </c>
       <c r="B73" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="C73">
         <v>408848.231299999</v>
@@ -3734,13 +3734,13 @@
         <v>296</v>
       </c>
       <c r="B1" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="C1" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="D1" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="E1" t="s">
         <v>0</v>
@@ -3751,7 +3751,7 @@
         <v>61</v>
       </c>
       <c r="B2" t="s">
-        <v>529</v>
+        <v>527</v>
       </c>
       <c r="C2">
         <v>408702.95299999899</v>
@@ -3768,7 +3768,7 @@
         <v>62</v>
       </c>
       <c r="B3" t="s">
-        <v>528</v>
+        <v>526</v>
       </c>
       <c r="C3">
         <v>408702.35950000002</v>
@@ -3785,7 +3785,7 @@
         <v>63</v>
       </c>
       <c r="B4" t="s">
-        <v>527</v>
+        <v>525</v>
       </c>
       <c r="C4">
         <v>408701.76500000001</v>
@@ -3802,7 +3802,7 @@
         <v>64</v>
       </c>
       <c r="B5" t="s">
-        <v>526</v>
+        <v>524</v>
       </c>
       <c r="C5">
         <v>408701.14669999899</v>
@@ -3819,7 +3819,7 @@
         <v>57</v>
       </c>
       <c r="B6" t="s">
-        <v>525</v>
+        <v>523</v>
       </c>
       <c r="C6">
         <v>408717.2047</v>
@@ -3836,7 +3836,7 @@
         <v>58</v>
       </c>
       <c r="B7" t="s">
-        <v>524</v>
+        <v>522</v>
       </c>
       <c r="C7">
         <v>408716.59240000002</v>
@@ -3853,7 +3853,7 @@
         <v>59</v>
       </c>
       <c r="B8" t="s">
-        <v>523</v>
+        <v>521</v>
       </c>
       <c r="C8">
         <v>408715.98029999901</v>
@@ -3870,7 +3870,7 @@
         <v>60</v>
       </c>
       <c r="B9" t="s">
-        <v>522</v>
+        <v>520</v>
       </c>
       <c r="C9">
         <v>408715.38030000002</v>
@@ -3887,7 +3887,7 @@
         <v>53</v>
       </c>
       <c r="B10" t="s">
-        <v>521</v>
+        <v>519</v>
       </c>
       <c r="C10">
         <v>408731.41739999899</v>
@@ -3904,7 +3904,7 @@
         <v>54</v>
       </c>
       <c r="B11" t="s">
-        <v>520</v>
+        <v>518</v>
       </c>
       <c r="C11">
         <v>408730.80660000001</v>
@@ -3921,7 +3921,7 @@
         <v>55</v>
       </c>
       <c r="B12" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="C12">
         <v>408730.19</v>
@@ -3938,7 +3938,7 @@
         <v>56</v>
       </c>
       <c r="B13" t="s">
-        <v>518</v>
+        <v>516</v>
       </c>
       <c r="C13">
         <v>408729.61050000001</v>
@@ -3955,7 +3955,7 @@
         <v>49</v>
       </c>
       <c r="B14" t="s">
-        <v>517</v>
+        <v>515</v>
       </c>
       <c r="C14">
         <v>408745.63719999901</v>
@@ -3972,7 +3972,7 @@
         <v>50</v>
       </c>
       <c r="B15" t="s">
-        <v>516</v>
+        <v>514</v>
       </c>
       <c r="C15">
         <v>408745.02610000002</v>
@@ -3989,7 +3989,7 @@
         <v>51</v>
       </c>
       <c r="B16" t="s">
-        <v>515</v>
+        <v>513</v>
       </c>
       <c r="C16">
         <v>408744.41419999901</v>
@@ -4006,7 +4006,7 @@
         <v>52</v>
       </c>
       <c r="B17" t="s">
-        <v>514</v>
+        <v>512</v>
       </c>
       <c r="C17">
         <v>408743.81449999899</v>
@@ -4023,7 +4023,7 @@
         <v>45</v>
       </c>
       <c r="B18" t="s">
-        <v>513</v>
+        <v>511</v>
       </c>
       <c r="C18">
         <v>408759.7758</v>
@@ -4040,7 +4040,7 @@
         <v>46</v>
       </c>
       <c r="B19" t="s">
-        <v>512</v>
+        <v>510</v>
       </c>
       <c r="C19">
         <v>408759.1692</v>
@@ -4057,7 +4057,7 @@
         <v>47</v>
       </c>
       <c r="B20" t="s">
-        <v>511</v>
+        <v>509</v>
       </c>
       <c r="C20">
         <v>408758.57179999899</v>
@@ -4074,7 +4074,7 @@
         <v>48</v>
       </c>
       <c r="B21" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="C21">
         <v>408757.959299999</v>
@@ -4091,7 +4091,7 @@
         <v>41</v>
       </c>
       <c r="B22" t="s">
-        <v>509</v>
+        <v>507</v>
       </c>
       <c r="C22">
         <v>408773.99790000002</v>
@@ -4108,7 +4108,7 @@
         <v>42</v>
       </c>
       <c r="B23" t="s">
-        <v>508</v>
+        <v>506</v>
       </c>
       <c r="C23">
         <v>408773.39649999898</v>
@@ -4125,7 +4125,7 @@
         <v>43</v>
       </c>
       <c r="B24" t="s">
-        <v>507</v>
+        <v>505</v>
       </c>
       <c r="C24">
         <v>408772.784099999</v>
@@ -4142,7 +4142,7 @@
         <v>44</v>
       </c>
       <c r="B25" t="s">
-        <v>506</v>
+        <v>504</v>
       </c>
       <c r="C25">
         <v>408772.17050000001</v>
@@ -4159,7 +4159,7 @@
         <v>37</v>
       </c>
       <c r="B26" t="s">
-        <v>505</v>
+        <v>503</v>
       </c>
       <c r="C26">
         <v>408788.22350000002</v>
@@ -4176,7 +4176,7 @@
         <v>38</v>
       </c>
       <c r="B27" t="s">
-        <v>504</v>
+        <v>502</v>
       </c>
       <c r="C27">
         <v>408787.60700000002</v>
@@ -4193,7 +4193,7 @@
         <v>39</v>
       </c>
       <c r="B28" t="s">
-        <v>503</v>
+        <v>501</v>
       </c>
       <c r="C28">
         <v>408787.00040000002</v>
@@ -4210,7 +4210,7 @@
         <v>40</v>
       </c>
       <c r="B29" t="s">
-        <v>502</v>
+        <v>500</v>
       </c>
       <c r="C29">
         <v>408786.40159999899</v>
@@ -4227,7 +4227,7 @@
         <v>33</v>
       </c>
       <c r="B30" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="C30">
         <v>408802.449499999</v>
@@ -4244,7 +4244,7 @@
         <v>34</v>
       </c>
       <c r="B31" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="C31">
         <v>408801.83819999901</v>
@@ -4261,7 +4261,7 @@
         <v>35</v>
       </c>
       <c r="B32" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="C32">
         <v>408801.21379999898</v>
@@ -4278,7 +4278,7 @@
         <v>36</v>
       </c>
       <c r="B33" t="s">
-        <v>498</v>
+        <v>496</v>
       </c>
       <c r="C33">
         <v>408800.62819999899</v>
@@ -4295,7 +4295,7 @@
         <v>29</v>
       </c>
       <c r="B34" t="s">
-        <v>497</v>
+        <v>495</v>
       </c>
       <c r="C34">
         <v>408816.59179999901</v>
@@ -4312,7 +4312,7 @@
         <v>30</v>
       </c>
       <c r="B35" t="s">
-        <v>496</v>
+        <v>494</v>
       </c>
       <c r="C35">
         <v>408815.986199999</v>
@@ -4329,7 +4329,7 @@
         <v>31</v>
       </c>
       <c r="B36" t="s">
-        <v>495</v>
+        <v>493</v>
       </c>
       <c r="C36">
         <v>408815.39</v>
@@ -4346,7 +4346,7 @@
         <v>32</v>
       </c>
       <c r="B37" t="s">
-        <v>494</v>
+        <v>492</v>
       </c>
       <c r="C37">
         <v>408814.777</v>
@@ -4363,7 +4363,7 @@
         <v>25</v>
       </c>
       <c r="B38" t="s">
-        <v>493</v>
+        <v>491</v>
       </c>
       <c r="C38">
         <v>408830.81489999901</v>
@@ -4380,7 +4380,7 @@
         <v>26</v>
       </c>
       <c r="B39" t="s">
-        <v>492</v>
+        <v>490</v>
       </c>
       <c r="C39">
         <v>408830.206899999</v>
@@ -4397,7 +4397,7 @@
         <v>27</v>
       </c>
       <c r="B40" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
       <c r="C40">
         <v>408829.59519999899</v>
@@ -4414,7 +4414,7 @@
         <v>28</v>
       </c>
       <c r="B41" t="s">
-        <v>490</v>
+        <v>488</v>
       </c>
       <c r="C41">
         <v>408828.99920000002</v>
@@ -4431,7 +4431,7 @@
         <v>21</v>
       </c>
       <c r="B42" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
       <c r="C42">
         <v>408845.03460000001</v>
@@ -4448,7 +4448,7 @@
         <v>22</v>
       </c>
       <c r="B43" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
       <c r="C43">
         <v>408844.4375</v>
@@ -4465,7 +4465,7 @@
         <v>23</v>
       </c>
       <c r="B44" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
       <c r="C44">
         <v>408843.829399999</v>
@@ -4482,7 +4482,7 @@
         <v>24</v>
       </c>
       <c r="B45" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="C45">
         <v>408843.20490000001</v>
@@ -4499,7 +4499,7 @@
         <v>17</v>
       </c>
       <c r="B46" t="s">
-        <v>485</v>
+        <v>483</v>
       </c>
       <c r="C46">
         <v>408859.25290000002</v>
@@ -4516,7 +4516,7 @@
         <v>18</v>
       </c>
       <c r="B47" t="s">
-        <v>484</v>
+        <v>482</v>
       </c>
       <c r="C47">
         <v>408858.64659999899</v>
@@ -4533,7 +4533,7 @@
         <v>19</v>
       </c>
       <c r="B48" t="s">
-        <v>483</v>
+        <v>481</v>
       </c>
       <c r="C48">
         <v>408858.0344</v>
@@ -4550,7 +4550,7 @@
         <v>20</v>
       </c>
       <c r="B49" t="s">
-        <v>482</v>
+        <v>480</v>
       </c>
       <c r="C49">
         <v>408857.44079999899</v>
@@ -4580,211 +4580,211 @@
         <v>295</v>
       </c>
       <c r="C1" t="s">
+        <v>528</v>
+      </c>
+      <c r="D1" t="s">
+        <v>529</v>
+      </c>
+      <c r="E1" t="s">
         <v>530</v>
       </c>
-      <c r="D1" t="s">
+      <c r="F1" t="s">
         <v>339</v>
       </c>
-      <c r="E1" t="s">
+      <c r="G1" t="s">
         <v>340</v>
       </c>
-      <c r="F1" t="s">
+      <c r="H1" t="s">
         <v>341</v>
       </c>
-      <c r="G1" t="s">
+      <c r="I1" t="s">
         <v>342</v>
       </c>
-      <c r="H1" t="s">
+      <c r="J1" t="s">
         <v>343</v>
       </c>
-      <c r="I1" t="s">
+      <c r="K1" t="s">
         <v>344</v>
       </c>
-      <c r="J1" t="s">
+      <c r="L1" t="s">
         <v>345</v>
       </c>
-      <c r="K1" t="s">
+      <c r="M1" t="s">
         <v>346</v>
       </c>
-      <c r="L1" t="s">
+      <c r="N1" t="s">
         <v>347</v>
       </c>
-      <c r="M1" t="s">
+      <c r="O1" t="s">
         <v>348</v>
       </c>
-      <c r="N1" t="s">
+      <c r="P1" t="s">
         <v>349</v>
       </c>
-      <c r="O1" t="s">
+      <c r="Q1" t="s">
         <v>350</v>
       </c>
-      <c r="P1" t="s">
+      <c r="R1" t="s">
         <v>351</v>
       </c>
-      <c r="Q1" t="s">
+      <c r="S1" t="s">
         <v>352</v>
       </c>
-      <c r="R1" t="s">
+      <c r="T1" t="s">
         <v>353</v>
       </c>
-      <c r="S1" t="s">
+      <c r="U1" t="s">
         <v>354</v>
       </c>
-      <c r="T1" t="s">
+      <c r="V1" t="s">
         <v>355</v>
       </c>
-      <c r="U1" t="s">
+      <c r="W1" t="s">
         <v>356</v>
       </c>
-      <c r="V1" t="s">
+      <c r="X1" t="s">
         <v>357</v>
       </c>
-      <c r="W1" t="s">
+      <c r="Y1" t="s">
         <v>358</v>
       </c>
-      <c r="X1" t="s">
+      <c r="Z1" t="s">
         <v>359</v>
       </c>
-      <c r="Y1" t="s">
+      <c r="AA1" t="s">
         <v>360</v>
       </c>
-      <c r="Z1" t="s">
+      <c r="AB1" t="s">
         <v>361</v>
       </c>
-      <c r="AA1" t="s">
+      <c r="AC1" t="s">
         <v>362</v>
       </c>
-      <c r="AB1" t="s">
+      <c r="AD1" t="s">
         <v>363</v>
       </c>
-      <c r="AC1" t="s">
+      <c r="AE1" t="s">
         <v>364</v>
       </c>
-      <c r="AD1" t="s">
+      <c r="AF1" t="s">
         <v>365</v>
       </c>
-      <c r="AE1" t="s">
+      <c r="AG1" t="s">
         <v>366</v>
       </c>
-      <c r="AF1" t="s">
+      <c r="AH1" t="s">
         <v>367</v>
       </c>
-      <c r="AG1" t="s">
+      <c r="AI1" t="s">
         <v>368</v>
       </c>
-      <c r="AH1" t="s">
+      <c r="AJ1" t="s">
         <v>369</v>
       </c>
-      <c r="AI1" t="s">
+      <c r="AK1" t="s">
         <v>370</v>
       </c>
-      <c r="AJ1" t="s">
+      <c r="AL1" t="s">
         <v>371</v>
       </c>
-      <c r="AK1" t="s">
+      <c r="AM1" t="s">
         <v>372</v>
       </c>
-      <c r="AL1" t="s">
+      <c r="AN1" t="s">
         <v>373</v>
       </c>
-      <c r="AM1" t="s">
+      <c r="AO1" t="s">
         <v>374</v>
       </c>
-      <c r="AN1" t="s">
+      <c r="AP1" t="s">
         <v>375</v>
       </c>
-      <c r="AO1" t="s">
+      <c r="AQ1" t="s">
         <v>376</v>
       </c>
-      <c r="AP1" t="s">
+      <c r="AR1" t="s">
         <v>377</v>
       </c>
-      <c r="AQ1" t="s">
+      <c r="AS1" t="s">
         <v>378</v>
       </c>
-      <c r="AR1" t="s">
+      <c r="AT1" t="s">
         <v>379</v>
       </c>
-      <c r="AS1" t="s">
+      <c r="AU1" t="s">
         <v>380</v>
       </c>
-      <c r="AT1" t="s">
+      <c r="AV1" t="s">
         <v>381</v>
       </c>
-      <c r="AU1" t="s">
+      <c r="AW1" t="s">
         <v>382</v>
       </c>
-      <c r="AV1" t="s">
+      <c r="AX1" t="s">
         <v>383</v>
       </c>
-      <c r="AW1" t="s">
+      <c r="AY1" t="s">
         <v>384</v>
       </c>
-      <c r="AX1" t="s">
+      <c r="AZ1" t="s">
         <v>385</v>
       </c>
-      <c r="AY1" t="s">
+      <c r="BA1" t="s">
         <v>386</v>
       </c>
-      <c r="AZ1" t="s">
+      <c r="BB1" t="s">
         <v>387</v>
       </c>
-      <c r="BA1" t="s">
+      <c r="BC1" t="s">
         <v>388</v>
       </c>
-      <c r="BB1" t="s">
+      <c r="BD1" t="s">
         <v>389</v>
       </c>
-      <c r="BC1" t="s">
+      <c r="BE1" t="s">
         <v>390</v>
       </c>
-      <c r="BD1" t="s">
+      <c r="BF1" t="s">
         <v>391</v>
       </c>
-      <c r="BE1" t="s">
+      <c r="BG1" t="s">
         <v>392</v>
       </c>
-      <c r="BF1" t="s">
+      <c r="BH1" t="s">
         <v>393</v>
       </c>
-      <c r="BG1" t="s">
+      <c r="BI1" t="s">
         <v>394</v>
       </c>
-      <c r="BH1" t="s">
+      <c r="BJ1" t="s">
         <v>395</v>
       </c>
-      <c r="BI1" t="s">
+      <c r="BK1" t="s">
         <v>396</v>
       </c>
-      <c r="BJ1" t="s">
+      <c r="BL1" t="s">
         <v>397</v>
       </c>
-      <c r="BK1" t="s">
+      <c r="BM1" t="s">
         <v>398</v>
       </c>
-      <c r="BL1" t="s">
+      <c r="BN1" t="s">
         <v>399</v>
       </c>
-      <c r="BM1" t="s">
+      <c r="BO1" t="s">
         <v>400</v>
       </c>
-      <c r="BN1" t="s">
+      <c r="BP1" t="s">
         <v>401</v>
       </c>
-      <c r="BO1" t="s">
+      <c r="BQ1" t="s">
         <v>402</v>
       </c>
-      <c r="BP1" t="s">
+      <c r="BR1" t="s">
         <v>403</v>
       </c>
-      <c r="BQ1" t="s">
+      <c r="BS1" t="s">
         <v>404</v>
-      </c>
-      <c r="BR1" t="s">
-        <v>405</v>
-      </c>
-      <c r="BS1" t="s">
-        <v>406</v>
       </c>
     </row>
     <row r="2" spans="1:71" x14ac:dyDescent="0.25">
@@ -65513,211 +65513,211 @@
         <v>0</v>
       </c>
       <c r="C1" t="s">
+        <v>528</v>
+      </c>
+      <c r="D1" t="s">
+        <v>529</v>
+      </c>
+      <c r="E1" t="s">
         <v>530</v>
       </c>
-      <c r="D1" t="s">
+      <c r="F1" t="s">
         <v>339</v>
       </c>
-      <c r="E1" t="s">
+      <c r="G1" t="s">
         <v>340</v>
       </c>
-      <c r="F1" t="s">
+      <c r="H1" t="s">
         <v>341</v>
       </c>
-      <c r="G1" t="s">
+      <c r="I1" t="s">
         <v>342</v>
       </c>
-      <c r="H1" t="s">
+      <c r="J1" t="s">
         <v>343</v>
       </c>
-      <c r="I1" t="s">
+      <c r="K1" t="s">
         <v>344</v>
       </c>
-      <c r="J1" t="s">
+      <c r="L1" t="s">
         <v>345</v>
       </c>
-      <c r="K1" t="s">
+      <c r="M1" t="s">
         <v>346</v>
       </c>
-      <c r="L1" t="s">
+      <c r="N1" t="s">
         <v>347</v>
       </c>
-      <c r="M1" t="s">
+      <c r="O1" t="s">
         <v>348</v>
       </c>
-      <c r="N1" t="s">
+      <c r="P1" t="s">
         <v>349</v>
       </c>
-      <c r="O1" t="s">
+      <c r="Q1" t="s">
         <v>350</v>
       </c>
-      <c r="P1" t="s">
+      <c r="R1" t="s">
         <v>351</v>
       </c>
-      <c r="Q1" t="s">
+      <c r="S1" t="s">
         <v>352</v>
       </c>
-      <c r="R1" t="s">
+      <c r="T1" t="s">
         <v>353</v>
       </c>
-      <c r="S1" t="s">
+      <c r="U1" t="s">
         <v>354</v>
       </c>
-      <c r="T1" t="s">
+      <c r="V1" t="s">
         <v>355</v>
       </c>
-      <c r="U1" t="s">
+      <c r="W1" t="s">
         <v>356</v>
       </c>
-      <c r="V1" t="s">
+      <c r="X1" t="s">
         <v>357</v>
       </c>
-      <c r="W1" t="s">
+      <c r="Y1" t="s">
         <v>358</v>
       </c>
-      <c r="X1" t="s">
+      <c r="Z1" t="s">
         <v>359</v>
       </c>
-      <c r="Y1" t="s">
+      <c r="AA1" t="s">
         <v>360</v>
       </c>
-      <c r="Z1" t="s">
+      <c r="AB1" t="s">
         <v>361</v>
       </c>
-      <c r="AA1" t="s">
+      <c r="AC1" t="s">
         <v>362</v>
       </c>
-      <c r="AB1" t="s">
+      <c r="AD1" t="s">
         <v>363</v>
       </c>
-      <c r="AC1" t="s">
+      <c r="AE1" t="s">
         <v>364</v>
       </c>
-      <c r="AD1" t="s">
+      <c r="AF1" t="s">
         <v>365</v>
       </c>
-      <c r="AE1" t="s">
+      <c r="AG1" t="s">
         <v>366</v>
       </c>
-      <c r="AF1" t="s">
+      <c r="AH1" t="s">
         <v>367</v>
       </c>
-      <c r="AG1" t="s">
+      <c r="AI1" t="s">
         <v>368</v>
       </c>
-      <c r="AH1" t="s">
+      <c r="AJ1" t="s">
         <v>369</v>
       </c>
-      <c r="AI1" t="s">
+      <c r="AK1" t="s">
         <v>370</v>
       </c>
-      <c r="AJ1" t="s">
+      <c r="AL1" t="s">
         <v>371</v>
       </c>
-      <c r="AK1" t="s">
+      <c r="AM1" t="s">
         <v>372</v>
       </c>
-      <c r="AL1" t="s">
+      <c r="AN1" t="s">
         <v>373</v>
       </c>
-      <c r="AM1" t="s">
+      <c r="AO1" t="s">
         <v>374</v>
       </c>
-      <c r="AN1" t="s">
+      <c r="AP1" t="s">
         <v>375</v>
       </c>
-      <c r="AO1" t="s">
+      <c r="AQ1" t="s">
         <v>376</v>
       </c>
-      <c r="AP1" t="s">
+      <c r="AR1" t="s">
         <v>377</v>
       </c>
-      <c r="AQ1" t="s">
+      <c r="AS1" t="s">
         <v>378</v>
       </c>
-      <c r="AR1" t="s">
+      <c r="AT1" t="s">
         <v>379</v>
       </c>
-      <c r="AS1" t="s">
+      <c r="AU1" t="s">
         <v>380</v>
       </c>
-      <c r="AT1" t="s">
+      <c r="AV1" t="s">
         <v>381</v>
       </c>
-      <c r="AU1" t="s">
+      <c r="AW1" t="s">
         <v>382</v>
       </c>
-      <c r="AV1" t="s">
+      <c r="AX1" t="s">
         <v>383</v>
       </c>
-      <c r="AW1" t="s">
+      <c r="AY1" t="s">
         <v>384</v>
       </c>
-      <c r="AX1" t="s">
+      <c r="AZ1" t="s">
         <v>385</v>
       </c>
-      <c r="AY1" t="s">
+      <c r="BA1" t="s">
         <v>386</v>
       </c>
-      <c r="AZ1" t="s">
+      <c r="BB1" t="s">
         <v>387</v>
       </c>
-      <c r="BA1" t="s">
+      <c r="BC1" t="s">
         <v>388</v>
       </c>
-      <c r="BB1" t="s">
+      <c r="BD1" t="s">
         <v>389</v>
       </c>
-      <c r="BC1" t="s">
+      <c r="BE1" t="s">
         <v>390</v>
       </c>
-      <c r="BD1" t="s">
+      <c r="BF1" t="s">
         <v>391</v>
       </c>
-      <c r="BE1" t="s">
+      <c r="BG1" t="s">
         <v>392</v>
       </c>
-      <c r="BF1" t="s">
+      <c r="BH1" t="s">
         <v>393</v>
       </c>
-      <c r="BG1" t="s">
+      <c r="BI1" t="s">
         <v>394</v>
       </c>
-      <c r="BH1" t="s">
+      <c r="BJ1" t="s">
         <v>395</v>
       </c>
-      <c r="BI1" t="s">
+      <c r="BK1" t="s">
         <v>396</v>
       </c>
-      <c r="BJ1" t="s">
+      <c r="BL1" t="s">
         <v>397</v>
       </c>
-      <c r="BK1" t="s">
+      <c r="BM1" t="s">
         <v>398</v>
       </c>
-      <c r="BL1" t="s">
+      <c r="BN1" t="s">
         <v>399</v>
       </c>
-      <c r="BM1" t="s">
+      <c r="BO1" t="s">
         <v>400</v>
       </c>
-      <c r="BN1" t="s">
+      <c r="BP1" t="s">
         <v>401</v>
       </c>
-      <c r="BO1" t="s">
+      <c r="BQ1" t="s">
         <v>402</v>
       </c>
-      <c r="BP1" t="s">
+      <c r="BR1" t="s">
         <v>403</v>
       </c>
-      <c r="BQ1" t="s">
+      <c r="BS1" t="s">
         <v>404</v>
-      </c>
-      <c r="BR1" t="s">
-        <v>405</v>
-      </c>
-      <c r="BS1" t="s">
-        <v>406</v>
       </c>
     </row>
     <row r="2" spans="1:71" x14ac:dyDescent="0.25">
